--- a/web/files/九龙-将军澳-海瑅湾 II.xlsx
+++ b/web/files/九龙-将军澳-海瑅湾 II.xlsx
@@ -54117,7 +54117,7 @@
       </c>
       <c r="G792" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="H792" s="5" t="n">
@@ -54373,7 +54373,7 @@
       </c>
       <c r="G796" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="H796" s="5" t="n">
@@ -56003,7 +56003,7 @@
       </c>
       <c r="G821" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="H821" s="5" t="n">
@@ -60039,7 +60039,7 @@
       </c>
       <c r="G883" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="H883" s="5" t="n">
@@ -95188,7 +95188,7 @@
           <t>D | 445呎 (2房)
 $712万
 $15,991/呎
-(26年-08月-09日)</t>
+(26年-08月-26日)</t>
         </is>
       </c>
       <c r="F40" s="23" t="inlineStr">
@@ -95243,7 +95243,7 @@
           <t>E | 464呎 (2房)
 $722万
 $15,571/呎
-(26年-08月-09日)</t>
+(26年-08月-26日)</t>
         </is>
       </c>
     </row>
@@ -95478,7 +95478,7 @@
           <t>E | 464呎 (2房)
 $716万
 $15,432/呎
-(26年-08月-08日)</t>
+(26年-08月-26日)</t>
         </is>
       </c>
     </row>
@@ -96026,7 +96026,7 @@
           <t>C | 488呎 (2房)
 $726万
 $14,885/呎
-(26年-08月-12日)</t>
+(26年-08月-26日)</t>
         </is>
       </c>
       <c r="E58" s="23" t="inlineStr">

--- a/web/files/九龙-将军澳-海瑅湾 II.xlsx
+++ b/web/files/九龙-将军澳-海瑅湾 II.xlsx
@@ -23,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -129,13 +129,19 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
       <color rgb="00660000"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="00004D00"/>
+      <color rgb="00000000"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -215,7 +221,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -283,10 +289,13 @@
     <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6378,7 +6387,7 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
@@ -6712,7 +6721,7 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
@@ -7046,7 +7055,7 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
@@ -7248,7 +7257,7 @@
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
@@ -7380,7 +7389,7 @@
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
@@ -7582,7 +7591,7 @@
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G101" s="3" t="inlineStr">
@@ -7714,7 +7723,7 @@
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G103" s="3" t="inlineStr">
@@ -7916,7 +7925,7 @@
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
@@ -8716,7 +8725,7 @@
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr">
@@ -9252,7 +9261,7 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
@@ -9586,7 +9595,7 @@
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G131" s="3" t="inlineStr">
@@ -9920,7 +9929,7 @@
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
@@ -10254,7 +10263,7 @@
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G141" s="3" t="inlineStr">
@@ -11256,7 +11265,7 @@
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
@@ -11590,7 +11599,7 @@
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G161" s="3" t="inlineStr">
@@ -11924,7 +11933,7 @@
       </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G166" s="3" t="inlineStr">
@@ -12258,7 +12267,7 @@
       </c>
       <c r="F171" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G171" s="3" t="inlineStr">
@@ -12320,7 +12329,7 @@
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
@@ -12646,7 +12655,7 @@
       </c>
       <c r="F177" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G177" s="3" t="inlineStr">
@@ -12972,7 +12981,7 @@
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G182" s="3" t="inlineStr">
@@ -13236,7 +13245,7 @@
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G186" s="3" t="inlineStr">
@@ -13298,7 +13307,7 @@
       </c>
       <c r="F187" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G187" s="3" t="inlineStr">
@@ -13562,7 +13571,7 @@
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G191" s="3" t="inlineStr">
@@ -13624,7 +13633,7 @@
       </c>
       <c r="F192" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G192" s="3" t="inlineStr">
@@ -13888,7 +13897,7 @@
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G196" s="3" t="inlineStr">
@@ -14866,7 +14875,7 @@
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G211" s="3" t="inlineStr">
@@ -15192,7 +15201,7 @@
       </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G216" s="3" t="inlineStr">
@@ -15518,7 +15527,7 @@
       </c>
       <c r="F221" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G221" s="3" t="inlineStr">
@@ -15844,7 +15853,7 @@
       </c>
       <c r="F226" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G226" s="3" t="inlineStr">
@@ -16170,7 +16179,7 @@
       </c>
       <c r="F231" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G231" s="3" t="inlineStr">
@@ -16496,7 +16505,7 @@
       </c>
       <c r="F236" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G236" s="3" t="inlineStr">
@@ -16822,7 +16831,7 @@
       </c>
       <c r="F241" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G241" s="3" t="inlineStr">
@@ -17148,7 +17157,7 @@
       </c>
       <c r="F246" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G246" s="3" t="inlineStr">
@@ -17474,7 +17483,7 @@
       </c>
       <c r="F251" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G251" s="3" t="inlineStr">
@@ -17800,7 +17809,7 @@
       </c>
       <c r="F256" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G256" s="3" t="inlineStr">
@@ -18864,7 +18873,7 @@
       </c>
       <c r="F272" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G272" s="3" t="inlineStr">
@@ -18926,7 +18935,7 @@
       </c>
       <c r="F273" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G273" s="3" t="inlineStr">
@@ -26290,7 +26299,7 @@
       </c>
       <c r="F379" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G379" s="3" t="inlineStr">
@@ -26694,7 +26703,7 @@
       </c>
       <c r="F385" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G385" s="3" t="inlineStr">
@@ -27098,7 +27107,7 @@
       </c>
       <c r="F391" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G391" s="3" t="inlineStr">
@@ -27502,7 +27511,7 @@
       </c>
       <c r="F397" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G397" s="3" t="inlineStr">
@@ -27906,7 +27915,7 @@
       </c>
       <c r="F403" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G403" s="3" t="inlineStr">
@@ -28310,7 +28319,7 @@
       </c>
       <c r="F409" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G409" s="3" t="inlineStr">
@@ -28714,7 +28723,7 @@
       </c>
       <c r="F415" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G415" s="3" t="inlineStr">
@@ -29118,7 +29127,7 @@
       </c>
       <c r="F421" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G421" s="3" t="inlineStr">
@@ -29522,7 +29531,7 @@
       </c>
       <c r="F427" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G427" s="3" t="inlineStr">
@@ -29926,7 +29935,7 @@
       </c>
       <c r="F433" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G433" s="3" t="inlineStr">
@@ -30330,7 +30339,7 @@
       </c>
       <c r="F439" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G439" s="3" t="inlineStr">
@@ -31542,7 +31551,7 @@
       </c>
       <c r="F457" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G457" s="3" t="inlineStr">
@@ -35116,7 +35125,7 @@
       </c>
       <c r="F510" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G510" s="3" t="inlineStr">
@@ -35520,7 +35529,7 @@
       </c>
       <c r="F516" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G516" s="3" t="inlineStr">
@@ -35924,7 +35933,7 @@
       </c>
       <c r="F522" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G522" s="3" t="inlineStr">
@@ -36328,7 +36337,7 @@
       </c>
       <c r="F528" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G528" s="3" t="inlineStr">
@@ -36732,7 +36741,7 @@
       </c>
       <c r="F534" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G534" s="3" t="inlineStr">
@@ -37136,7 +37145,7 @@
       </c>
       <c r="F540" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G540" s="3" t="inlineStr">
@@ -37540,7 +37549,7 @@
       </c>
       <c r="F546" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G546" s="3" t="inlineStr">
@@ -37944,7 +37953,7 @@
       </c>
       <c r="F552" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G552" s="3" t="inlineStr">
@@ -38348,7 +38357,7 @@
       </c>
       <c r="F558" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G558" s="3" t="inlineStr">
@@ -38752,7 +38761,7 @@
       </c>
       <c r="F564" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G564" s="3" t="inlineStr">
@@ -39156,7 +39165,7 @@
       </c>
       <c r="F570" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G570" s="3" t="inlineStr">
@@ -39560,7 +39569,7 @@
       </c>
       <c r="F576" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G576" s="3" t="inlineStr">
@@ -39964,7 +39973,7 @@
       </c>
       <c r="F582" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G582" s="3" t="inlineStr">
@@ -40368,7 +40377,7 @@
       </c>
       <c r="F588" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G588" s="3" t="inlineStr">
@@ -40772,7 +40781,7 @@
       </c>
       <c r="F594" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G594" s="3" t="inlineStr">
@@ -47864,7 +47873,7 @@
       </c>
       <c r="F696" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G696" s="3" t="inlineStr">
@@ -47988,7 +47997,7 @@
       </c>
       <c r="F698" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G698" s="3" t="inlineStr">
@@ -48190,7 +48199,7 @@
       </c>
       <c r="F701" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G701" s="3" t="inlineStr">
@@ -48252,7 +48261,7 @@
       </c>
       <c r="F702" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G702" s="3" t="inlineStr">
@@ -48314,7 +48323,7 @@
       </c>
       <c r="F703" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G703" s="3" t="inlineStr">
@@ -48516,7 +48525,7 @@
       </c>
       <c r="F706" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G706" s="3" t="inlineStr">
@@ -48578,7 +48587,7 @@
       </c>
       <c r="F707" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G707" s="3" t="inlineStr">
@@ -48640,7 +48649,7 @@
       </c>
       <c r="F708" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G708" s="3" t="inlineStr">
@@ -48842,7 +48851,7 @@
       </c>
       <c r="F711" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G711" s="3" t="inlineStr">
@@ -48904,7 +48913,7 @@
       </c>
       <c r="F712" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G712" s="3" t="inlineStr">
@@ -48966,7 +48975,7 @@
       </c>
       <c r="F713" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G713" s="3" t="inlineStr">
@@ -49168,7 +49177,7 @@
       </c>
       <c r="F716" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G716" s="3" t="inlineStr">
@@ -49230,7 +49239,7 @@
       </c>
       <c r="F717" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G717" s="3" t="inlineStr">
@@ -49292,7 +49301,7 @@
       </c>
       <c r="F718" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G718" s="3" t="inlineStr">
@@ -49494,7 +49503,7 @@
       </c>
       <c r="F721" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G721" s="3" t="inlineStr">
@@ -49556,7 +49565,7 @@
       </c>
       <c r="F722" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G722" s="3" t="inlineStr">
@@ -49618,7 +49627,7 @@
       </c>
       <c r="F723" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G723" s="3" t="inlineStr">
@@ -49882,7 +49891,7 @@
       </c>
       <c r="F727" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G727" s="3" t="inlineStr">
@@ -49944,7 +49953,7 @@
       </c>
       <c r="F728" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G728" s="3" t="inlineStr">
@@ -50208,7 +50217,7 @@
       </c>
       <c r="F732" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G732" s="3" t="inlineStr">
@@ -50270,7 +50279,7 @@
       </c>
       <c r="F733" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G733" s="3" t="inlineStr">
@@ -50472,7 +50481,7 @@
       </c>
       <c r="F736" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G736" s="3" t="inlineStr">
@@ -50534,7 +50543,7 @@
       </c>
       <c r="F737" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G737" s="3" t="inlineStr">
@@ -50596,7 +50605,7 @@
       </c>
       <c r="F738" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G738" s="3" t="inlineStr">
@@ -50798,7 +50807,7 @@
       </c>
       <c r="F741" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G741" s="3" t="inlineStr">
@@ -50860,7 +50869,7 @@
       </c>
       <c r="F742" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G742" s="3" t="inlineStr">
@@ -50922,7 +50931,7 @@
       </c>
       <c r="F743" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G743" s="3" t="inlineStr">
@@ -51124,23 +51133,23 @@
       </c>
       <c r="F746" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G746" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="H746" s="5" t="n">
-        <v>8714000</v>
+        <v>7406900</v>
       </c>
       <c r="I746" s="5" t="n">
-        <v>18780</v>
+        <v>15963</v>
       </c>
       <c r="J746" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K746" s="5" t="n">
@@ -51151,7 +51160,7 @@
       </c>
       <c r="M746" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N746" s="3" t="inlineStr">
@@ -51186,7 +51195,7 @@
       </c>
       <c r="F747" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G747" s="3" t="inlineStr">
@@ -51248,7 +51257,7 @@
       </c>
       <c r="F748" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G748" s="3" t="inlineStr">
@@ -51512,7 +51521,7 @@
       </c>
       <c r="F752" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G752" s="3" t="inlineStr">
@@ -51574,7 +51583,7 @@
       </c>
       <c r="F753" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G753" s="3" t="inlineStr">
@@ -51838,7 +51847,7 @@
       </c>
       <c r="F757" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G757" s="3" t="inlineStr">
@@ -51900,7 +51909,7 @@
       </c>
       <c r="F758" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G758" s="3" t="inlineStr">
@@ -52164,7 +52173,7 @@
       </c>
       <c r="F762" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G762" s="3" t="inlineStr">
@@ -52226,7 +52235,7 @@
       </c>
       <c r="F763" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G763" s="3" t="inlineStr">
@@ -52490,7 +52499,7 @@
       </c>
       <c r="F767" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G767" s="3" t="inlineStr">
@@ -52552,7 +52561,7 @@
       </c>
       <c r="F768" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G768" s="3" t="inlineStr">
@@ -52816,7 +52825,7 @@
       </c>
       <c r="F772" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G772" s="3" t="inlineStr">
@@ -53142,7 +53151,7 @@
       </c>
       <c r="F777" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G777" s="3" t="inlineStr">
@@ -55858,38 +55867,30 @@
       </c>
       <c r="F819" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G819" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H819" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I819" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="H819" s="5" t="n">
+        <v>11155000</v>
+      </c>
+      <c r="I819" s="5" t="n">
+        <v>18530</v>
       </c>
       <c r="J819" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K819" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L819" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K819" s="5" t="n">
+        <v>11155000</v>
+      </c>
+      <c r="L819" s="5" t="n">
+        <v>18530</v>
       </c>
       <c r="M819" s="3" t="inlineStr">
         <is>
@@ -55898,7 +55899,7 @@
       </c>
       <c r="N819" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -56391,7 +56392,7 @@
       </c>
       <c r="G827" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H827" s="5" t="n">
@@ -58611,7 +58612,7 @@
       </c>
       <c r="G861" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H861" s="5" t="n">
@@ -59258,7 +59259,7 @@
       </c>
       <c r="F871" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G871" s="3" t="inlineStr">
@@ -59320,7 +59321,7 @@
       </c>
       <c r="F872" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G872" s="3" t="inlineStr">
@@ -59584,7 +59585,7 @@
       </c>
       <c r="F876" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G876" s="3" t="inlineStr">
@@ -59910,7 +59911,7 @@
       </c>
       <c r="F881" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G881" s="3" t="inlineStr">
@@ -60236,7 +60237,7 @@
       </c>
       <c r="F886" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G886" s="3" t="inlineStr">
@@ -60298,7 +60299,7 @@
       </c>
       <c r="F887" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G887" s="3" t="inlineStr">
@@ -61332,7 +61333,7 @@
       </c>
       <c r="F902" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G902" s="3" t="inlineStr">
@@ -61814,7 +61815,7 @@
       </c>
       <c r="F909" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G909" s="3" t="inlineStr">
@@ -62296,7 +62297,7 @@
       </c>
       <c r="F916" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G916" s="3" t="inlineStr">
@@ -62778,7 +62779,7 @@
       </c>
       <c r="F923" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G923" s="3" t="inlineStr">
@@ -63260,7 +63261,7 @@
       </c>
       <c r="F930" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G930" s="3" t="inlineStr">
@@ -63742,7 +63743,7 @@
       </c>
       <c r="F937" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G937" s="3" t="inlineStr">
@@ -64224,7 +64225,7 @@
       </c>
       <c r="F944" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G944" s="3" t="inlineStr">
@@ -64706,7 +64707,7 @@
       </c>
       <c r="F951" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G951" s="3" t="inlineStr">
@@ -65188,7 +65189,7 @@
       </c>
       <c r="F958" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G958" s="3" t="inlineStr">
@@ -65670,7 +65671,7 @@
       </c>
       <c r="F965" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G965" s="3" t="inlineStr">
@@ -66152,7 +66153,7 @@
       </c>
       <c r="F972" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G972" s="3" t="inlineStr">
@@ -66634,7 +66635,7 @@
       </c>
       <c r="F979" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G979" s="3" t="inlineStr">
@@ -67116,7 +67117,7 @@
       </c>
       <c r="F986" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G986" s="3" t="inlineStr">
@@ -67598,7 +67599,7 @@
       </c>
       <c r="F993" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G993" s="3" t="inlineStr">
@@ -68080,7 +68081,7 @@
       </c>
       <c r="F1000" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1000" s="3" t="inlineStr">
@@ -72898,7 +72899,7 @@
       </c>
       <c r="F1071" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1071" s="3" t="inlineStr">
@@ -73372,7 +73373,7 @@
       </c>
       <c r="F1078" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1078" s="3" t="inlineStr">
@@ -73846,7 +73847,7 @@
       </c>
       <c r="F1085" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1085" s="3" t="inlineStr">
@@ -74320,7 +74321,7 @@
       </c>
       <c r="F1092" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1092" s="3" t="inlineStr">
@@ -74786,7 +74787,7 @@
       </c>
       <c r="F1099" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1099" s="3" t="inlineStr">
@@ -77590,7 +77591,7 @@
       </c>
       <c r="F1141" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1141" s="3" t="inlineStr">
@@ -78056,7 +78057,7 @@
       </c>
       <c r="F1148" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1148" s="3" t="inlineStr">
@@ -78522,7 +78523,7 @@
       </c>
       <c r="F1155" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1155" s="3" t="inlineStr">
@@ -78988,7 +78989,7 @@
       </c>
       <c r="F1162" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1162" s="3" t="inlineStr">
@@ -79454,7 +79455,7 @@
       </c>
       <c r="F1169" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1169" s="3" t="inlineStr">
@@ -79920,7 +79921,7 @@
       </c>
       <c r="F1176" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1176" s="3" t="inlineStr">
@@ -80386,7 +80387,7 @@
       </c>
       <c r="F1183" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1183" s="3" t="inlineStr">
@@ -80860,7 +80861,7 @@
       </c>
       <c r="F1190" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1190" s="3" t="inlineStr">
@@ -81334,7 +81335,7 @@
       </c>
       <c r="F1197" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1197" s="3" t="inlineStr">
@@ -81808,7 +81809,7 @@
       </c>
       <c r="F1204" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1204" s="3" t="inlineStr">
@@ -83906,7 +83907,7 @@
       </c>
       <c r="F1235" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G1235" s="3" t="inlineStr">
@@ -83976,7 +83977,7 @@
       </c>
       <c r="F1236" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G1236" s="3" t="inlineStr">
@@ -84380,7 +84381,7 @@
       </c>
       <c r="F1242" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G1242" s="3" t="inlineStr">
@@ -84450,7 +84451,7 @@
       </c>
       <c r="F1243" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G1243" s="3" t="inlineStr">
@@ -85802,7 +85803,7 @@
       </c>
       <c r="F1263" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G1263" s="3" t="inlineStr">
@@ -85872,7 +85873,7 @@
       </c>
       <c r="F1264" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G1264" s="3" t="inlineStr">
@@ -86074,7 +86075,7 @@
       </c>
       <c r="F1267" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1267" s="3" t="inlineStr">
@@ -86276,7 +86277,7 @@
       </c>
       <c r="F1270" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G1270" s="3" t="inlineStr">
@@ -86346,7 +86347,7 @@
       </c>
       <c r="F1271" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G1271" s="3" t="inlineStr">
@@ -86548,7 +86549,7 @@
       </c>
       <c r="F1274" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1274" s="3" t="inlineStr">
@@ -86750,7 +86751,7 @@
       </c>
       <c r="F1277" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G1277" s="3" t="inlineStr">
@@ -86820,7 +86821,7 @@
       </c>
       <c r="F1278" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G1278" s="3" t="inlineStr">
@@ -87497,12 +87498,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -88328,12 +88329,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E21" s="22" t="inlineStr">
+      <c r="E21" s="23" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $872万
 $19,552/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -88375,12 +88376,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E22" s="22" t="inlineStr">
+      <c r="E22" s="23" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $871万
 $19,520/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -88398,12 +88399,12 @@
           <t>49</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B23" s="23" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
 $1049万
 $22,222/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -88422,12 +88423,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E23" s="22" t="inlineStr">
+      <c r="E23" s="23" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $869万
 $19,491/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -88445,12 +88446,12 @@
           <t>48</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B24" s="23" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
 $1049万
 $22,222/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -88469,12 +88470,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E24" s="22" t="inlineStr">
+      <c r="E24" s="23" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $869万
 $19,491/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -88492,12 +88493,12 @@
           <t>47</t>
         </is>
       </c>
-      <c r="B25" s="22" t="inlineStr">
+      <c r="B25" s="23" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
 $1045万
 $22,136/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -88516,12 +88517,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E25" s="22" t="inlineStr">
+      <c r="E25" s="23" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $867万
 $19,433/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -88563,7 +88564,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E26" s="23" t="inlineStr">
+      <c r="E26" s="24" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $728万
@@ -88610,7 +88611,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E27" s="23" t="inlineStr">
+      <c r="E27" s="24" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $727万
@@ -88657,12 +88658,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E28" s="22" t="inlineStr">
+      <c r="E28" s="23" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $863万
 $19,345/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -88680,12 +88681,12 @@
           <t>42</t>
         </is>
       </c>
-      <c r="B29" s="22" t="inlineStr">
+      <c r="B29" s="23" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
 $1036万
 $21,960/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -88704,7 +88705,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E29" s="23" t="inlineStr">
+      <c r="E29" s="24" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $725万
@@ -88727,12 +88728,12 @@
           <t>41</t>
         </is>
       </c>
-      <c r="B30" s="22" t="inlineStr">
+      <c r="B30" s="23" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
 $1034万
 $21,917/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
@@ -88751,7 +88752,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E30" s="23" t="inlineStr">
+      <c r="E30" s="24" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $724万
@@ -88774,12 +88775,12 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B31" s="22" t="inlineStr">
+      <c r="B31" s="23" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
 $1032万
 $21,873/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -88798,7 +88799,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E31" s="23" t="inlineStr">
+      <c r="E31" s="24" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $723万
@@ -88821,7 +88822,54 @@
           <t>39</t>
         </is>
       </c>
-      <c r="B32" s="22" t="inlineStr">
+      <c r="B32" s="23" t="inlineStr">
+        <is>
+          <t>A | 472呎 (2房)
+$1030万
+$21,826/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>B | 567呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D32" s="20" t="inlineStr">
+        <is>
+          <t>C | 474呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E32" s="24" t="inlineStr">
+        <is>
+          <t>D | 446呎 (2房)
+$722万
+$16,184/呎
+(26年-08月-18日)</t>
+        </is>
+      </c>
+      <c r="F32" s="20" t="inlineStr">
+        <is>
+          <t>E | 460呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
 $1030万
@@ -88829,7 +88877,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="C32" s="20" t="inlineStr">
+      <c r="C33" s="20" t="inlineStr">
         <is>
           <t>B | 567呎 (2房)
 -
@@ -88837,7 +88885,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D32" s="20" t="inlineStr">
+      <c r="D33" s="20" t="inlineStr">
         <is>
           <t>C | 474呎 (2房)
 -
@@ -88845,54 +88893,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E32" s="23" t="inlineStr">
-        <is>
-          <t>D | 446呎 (2房)
-$722万
-$16,184/呎
-(26年-08月-18日)</t>
-        </is>
-      </c>
-      <c r="F32" s="20" t="inlineStr">
-        <is>
-          <t>E | 460呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="58" customHeight="1">
-      <c r="A33" s="19" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B33" s="22" t="inlineStr">
-        <is>
-          <t>A | 472呎 (2房)
-$1030万
-$21,826/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C33" s="20" t="inlineStr">
-        <is>
-          <t>B | 567呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D33" s="20" t="inlineStr">
-        <is>
-          <t>C | 474呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E33" s="23" t="inlineStr">
+      <c r="E33" s="24" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $722万
@@ -88939,7 +88940,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E34" s="23" t="inlineStr">
+      <c r="E34" s="24" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $720万
@@ -88962,12 +88963,12 @@
           <t>36</t>
         </is>
       </c>
-      <c r="B35" s="22" t="inlineStr">
+      <c r="B35" s="23" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
 $1024万
 $21,697/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C35" s="20" t="inlineStr">
@@ -88986,7 +88987,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E35" s="23" t="inlineStr">
+      <c r="E35" s="24" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $719万
@@ -89009,12 +89010,12 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B36" s="22" t="inlineStr">
+      <c r="B36" s="23" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
 $1022万
 $21,655/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C36" s="20" t="inlineStr">
@@ -89033,7 +89034,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E36" s="23" t="inlineStr">
+      <c r="E36" s="24" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $734万
@@ -89056,12 +89057,12 @@
           <t>33</t>
         </is>
       </c>
-      <c r="B37" s="22" t="inlineStr">
+      <c r="B37" s="23" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
 $1020万
 $21,610/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C37" s="20" t="inlineStr">
@@ -89080,7 +89081,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E37" s="23" t="inlineStr">
+      <c r="E37" s="24" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $716万
@@ -89103,12 +89104,12 @@
           <t>32</t>
         </is>
       </c>
-      <c r="B38" s="22" t="inlineStr">
+      <c r="B38" s="23" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
 $1018万
 $21,568/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C38" s="20" t="inlineStr">
@@ -89127,7 +89128,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E38" s="23" t="inlineStr">
+      <c r="E38" s="24" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $732万
@@ -89174,7 +89175,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E39" s="23" t="inlineStr">
+      <c r="E39" s="24" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $714万
@@ -89182,12 +89183,12 @@
 (26年-08月-11日)</t>
         </is>
       </c>
-      <c r="F39" s="22" t="inlineStr">
+      <c r="F39" s="23" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $889万
 $19,320/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -89221,7 +89222,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E40" s="23" t="inlineStr">
+      <c r="E40" s="24" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $730万
@@ -89229,12 +89230,12 @@
 (26年-08月-10日)</t>
         </is>
       </c>
-      <c r="F40" s="22" t="inlineStr">
+      <c r="F40" s="23" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $887万
 $19,280/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -89244,12 +89245,12 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B41" s="22" t="inlineStr">
+      <c r="B41" s="23" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
 $1012万
 $21,439/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C41" s="20" t="inlineStr">
@@ -89268,7 +89269,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E41" s="23" t="inlineStr">
+      <c r="E41" s="24" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $712万
@@ -89276,12 +89277,12 @@
 (26年-08月-13日)</t>
         </is>
       </c>
-      <c r="F41" s="22" t="inlineStr">
+      <c r="F41" s="23" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $885万
 $19,243/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -89291,12 +89292,12 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B42" s="22" t="inlineStr">
+      <c r="B42" s="23" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
 $1012万
 $21,439/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C42" s="20" t="inlineStr">
@@ -89315,7 +89316,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E42" s="23" t="inlineStr">
+      <c r="E42" s="24" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $712万
@@ -89323,12 +89324,12 @@
 (26年-08月-18日)</t>
         </is>
       </c>
-      <c r="F42" s="22" t="inlineStr">
+      <c r="F42" s="23" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $885万
 $19,243/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -89338,12 +89339,12 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B43" s="22" t="inlineStr">
+      <c r="B43" s="23" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
 $1008万
 $21,354/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C43" s="20" t="inlineStr">
@@ -89362,7 +89363,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E43" s="23" t="inlineStr">
+      <c r="E43" s="24" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $710万
@@ -89370,12 +89371,12 @@
 (26年-08月-14日)</t>
         </is>
       </c>
-      <c r="F43" s="22" t="inlineStr">
+      <c r="F43" s="23" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $882万
 $19,165/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -89409,7 +89410,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E44" s="23" t="inlineStr">
+      <c r="E44" s="24" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $726万
@@ -89417,7 +89418,7 @@
 (26年-08月-11日)</t>
         </is>
       </c>
-      <c r="F44" s="23" t="inlineStr">
+      <c r="F44" s="24" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $741万
@@ -89456,7 +89457,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E45" s="23" t="inlineStr">
+      <c r="E45" s="24" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $725万
@@ -89464,7 +89465,7 @@
 (26年-08月-11日)</t>
         </is>
       </c>
-      <c r="F45" s="23" t="inlineStr">
+      <c r="F45" s="24" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $739万
@@ -89479,12 +89480,12 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B46" s="22" t="inlineStr">
+      <c r="B46" s="23" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
 $1000万
 $21,184/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C46" s="20" t="inlineStr">
@@ -89503,7 +89504,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E46" s="23" t="inlineStr">
+      <c r="E46" s="24" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $706万
@@ -89511,7 +89512,7 @@
 (26年-08月-19日)</t>
         </is>
       </c>
-      <c r="F46" s="23" t="inlineStr">
+      <c r="F46" s="24" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $736万
@@ -89526,12 +89527,12 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B47" s="22" t="inlineStr">
+      <c r="B47" s="23" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
 $998万
 $21,142/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C47" s="20" t="inlineStr">
@@ -89550,7 +89551,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E47" s="23" t="inlineStr">
+      <c r="E47" s="24" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $705万
@@ -89558,7 +89559,7 @@
 (26年-08月-14日)</t>
         </is>
       </c>
-      <c r="F47" s="23" t="inlineStr">
+      <c r="F47" s="24" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $735万
@@ -89573,12 +89574,12 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B48" s="22" t="inlineStr">
+      <c r="B48" s="23" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
 $996万
 $21,100/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C48" s="20" t="inlineStr">
@@ -89597,7 +89598,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E48" s="23" t="inlineStr">
+      <c r="E48" s="24" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $704万
@@ -89605,7 +89606,7 @@
 (26年-08月-20日)</t>
         </is>
       </c>
-      <c r="F48" s="23" t="inlineStr">
+      <c r="F48" s="24" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $733万
@@ -89620,12 +89621,12 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B49" s="22" t="inlineStr">
+      <c r="B49" s="23" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
 $994万
 $21,057/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C49" s="20" t="inlineStr">
@@ -89644,7 +89645,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E49" s="23" t="inlineStr">
+      <c r="E49" s="24" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $703万
@@ -89652,7 +89653,7 @@
 (26年-08月-11日)</t>
         </is>
       </c>
-      <c r="F49" s="23" t="inlineStr">
+      <c r="F49" s="24" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $732万
@@ -89667,12 +89668,12 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B50" s="22" t="inlineStr">
+      <c r="B50" s="23" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
 $994万
 $21,057/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C50" s="20" t="inlineStr">
@@ -89691,7 +89692,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E50" s="23" t="inlineStr">
+      <c r="E50" s="24" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $719万
@@ -89699,7 +89700,7 @@
 (26年-08月-13日)</t>
         </is>
       </c>
-      <c r="F50" s="23" t="inlineStr">
+      <c r="F50" s="24" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $749万
@@ -89714,12 +89715,12 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B51" s="22" t="inlineStr">
+      <c r="B51" s="23" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
 $990万
 $20,975/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C51" s="20" t="inlineStr">
@@ -89738,7 +89739,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E51" s="23" t="inlineStr">
+      <c r="E51" s="24" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $717万
@@ -89746,7 +89747,7 @@
 (26年-08月-11日)</t>
         </is>
       </c>
-      <c r="F51" s="23" t="inlineStr">
+      <c r="F51" s="24" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $729万
@@ -89761,12 +89762,12 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B52" s="22" t="inlineStr">
+      <c r="B52" s="23" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
 $988万
 $20,932/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C52" s="20" t="inlineStr">
@@ -89785,7 +89786,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E52" s="23" t="inlineStr">
+      <c r="E52" s="24" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $699万
@@ -89793,7 +89794,7 @@
 (26年-08月-11日)</t>
         </is>
       </c>
-      <c r="F52" s="23" t="inlineStr">
+      <c r="F52" s="24" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $744万
@@ -89808,12 +89809,12 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B53" s="22" t="inlineStr">
+      <c r="B53" s="23" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
 $986万
 $20,890/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C53" s="20" t="inlineStr">
@@ -89832,7 +89833,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E53" s="23" t="inlineStr">
+      <c r="E53" s="24" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $698万
@@ -89840,7 +89841,7 @@
 (26年-08月-18日)</t>
         </is>
       </c>
-      <c r="F53" s="23" t="inlineStr">
+      <c r="F53" s="24" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $726万
@@ -89855,12 +89856,12 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B54" s="22" t="inlineStr">
+      <c r="B54" s="23" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
 $984万
 $20,847/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C54" s="20" t="inlineStr">
@@ -89879,7 +89880,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E54" s="23" t="inlineStr">
+      <c r="E54" s="24" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $714万
@@ -89887,7 +89888,7 @@
 (26年-08月-19日)</t>
         </is>
       </c>
-      <c r="F54" s="23" t="inlineStr">
+      <c r="F54" s="24" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $724万
@@ -89902,12 +89903,12 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B55" s="22" t="inlineStr">
+      <c r="B55" s="23" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
 $982万
 $20,807/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C55" s="20" t="inlineStr">
@@ -89926,7 +89927,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E55" s="23" t="inlineStr">
+      <c r="E55" s="24" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $696万
@@ -89934,7 +89935,7 @@
 (26年-08月-18日)</t>
         </is>
       </c>
-      <c r="F55" s="23" t="inlineStr">
+      <c r="F55" s="24" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $723万
@@ -89973,7 +89974,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E56" s="23" t="inlineStr">
+      <c r="E56" s="24" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $712万
@@ -89981,7 +89982,7 @@
 (26年-08月-15日)</t>
         </is>
       </c>
-      <c r="F56" s="23" t="inlineStr">
+      <c r="F56" s="24" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $738万
@@ -90020,7 +90021,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E57" s="23" t="inlineStr">
+      <c r="E57" s="24" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $694万
@@ -90028,7 +90029,7 @@
 (26年-08月-24日)</t>
         </is>
       </c>
-      <c r="F57" s="23" t="inlineStr">
+      <c r="F57" s="24" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $720万
@@ -90067,7 +90068,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E58" s="23" t="inlineStr">
+      <c r="E58" s="24" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $694万
@@ -90075,7 +90076,7 @@
 (26年-08月-24日)</t>
         </is>
       </c>
-      <c r="F58" s="23" t="inlineStr">
+      <c r="F58" s="24" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $720万
@@ -90114,20 +90115,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E59" s="22" t="inlineStr">
+      <c r="E59" s="23" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $822万
 $18,442/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F59" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F59" s="23" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $852万
 $18,524/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -90252,12 +90253,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>29</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -91216,12 +91217,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E21" s="22" t="inlineStr">
+      <c r="E21" s="23" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $1078万
 $19,458/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -91271,12 +91272,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E22" s="22" t="inlineStr">
+      <c r="E22" s="23" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $1076万
 $19,430/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -91326,12 +91327,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E23" s="22" t="inlineStr">
+      <c r="E23" s="23" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $1075万
 $19,399/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -91381,12 +91382,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E24" s="22" t="inlineStr">
+      <c r="E24" s="23" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $1075万
 $19,399/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -91436,12 +91437,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E25" s="22" t="inlineStr">
+      <c r="E25" s="23" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $1072万
 $19,341/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -91491,12 +91492,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E26" s="22" t="inlineStr">
+      <c r="E26" s="23" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $1070万
 $19,312/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -91546,12 +91547,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E27" s="22" t="inlineStr">
+      <c r="E27" s="23" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $1068万
 $19,285/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -91601,12 +91602,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E28" s="22" t="inlineStr">
+      <c r="E28" s="23" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $1067万
 $19,255/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -91656,12 +91657,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E29" s="22" t="inlineStr">
+      <c r="E29" s="23" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $1065万
 $19,226/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F29" s="22" t="inlineStr">
@@ -91711,12 +91712,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E30" s="22" t="inlineStr">
+      <c r="E30" s="23" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $1064万
 $19,197/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
@@ -91766,12 +91767,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E31" s="22" t="inlineStr">
+      <c r="E31" s="23" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $1062万
 $19,168/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F31" s="22" t="inlineStr">
@@ -91821,7 +91822,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E32" s="23" t="inlineStr">
+      <c r="E32" s="24" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $901万
@@ -91876,7 +91877,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E33" s="23" t="inlineStr">
+      <c r="E33" s="24" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $901万
@@ -91931,12 +91932,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E34" s="22" t="inlineStr">
+      <c r="E34" s="23" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $1057万
 $19,083/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F34" s="22" t="inlineStr">
@@ -91986,7 +91987,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E35" s="23" t="inlineStr">
+      <c r="E35" s="24" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $893万
@@ -92025,7 +92026,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C36" s="24" t="inlineStr">
+      <c r="C36" s="23" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
 招标单位
@@ -92041,7 +92042,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E36" s="23" t="inlineStr">
+      <c r="E36" s="24" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $896万
@@ -92080,7 +92081,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C37" s="24" t="inlineStr">
+      <c r="C37" s="23" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
 招标单位
@@ -92096,7 +92097,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E37" s="23" t="inlineStr">
+      <c r="E37" s="24" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $890万
@@ -92135,7 +92136,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C38" s="24" t="inlineStr">
+      <c r="C38" s="23" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
 招标单位
@@ -92151,7 +92152,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E38" s="23" t="inlineStr">
+      <c r="E38" s="24" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $889万
@@ -92190,7 +92191,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C39" s="24" t="inlineStr">
+      <c r="C39" s="23" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
 招标单位
@@ -92206,7 +92207,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E39" s="23" t="inlineStr">
+      <c r="E39" s="24" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $908万
@@ -92245,7 +92246,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C40" s="24" t="inlineStr">
+      <c r="C40" s="23" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
 招标单位
@@ -92261,7 +92262,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E40" s="23" t="inlineStr">
+      <c r="E40" s="24" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $886万
@@ -92300,7 +92301,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C41" s="24" t="inlineStr">
+      <c r="C41" s="23" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
 招标单位
@@ -92316,7 +92317,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E41" s="23" t="inlineStr">
+      <c r="E41" s="24" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $885万
@@ -92355,7 +92356,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C42" s="24" t="inlineStr">
+      <c r="C42" s="23" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
 招标单位
@@ -92371,7 +92372,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E42" s="23" t="inlineStr">
+      <c r="E42" s="24" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $906万
@@ -92410,7 +92411,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C43" s="24" t="inlineStr">
+      <c r="C43" s="23" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
 招标单位
@@ -92426,7 +92427,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E43" s="23" t="inlineStr">
+      <c r="E43" s="24" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $882万
@@ -92434,12 +92435,12 @@
 (26年-08月-14日)</t>
         </is>
       </c>
-      <c r="F43" s="22" t="inlineStr">
+      <c r="F43" s="23" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
 $872万
 $19,258/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="G43" s="20" t="inlineStr">
@@ -92465,7 +92466,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C44" s="24" t="inlineStr">
+      <c r="C44" s="23" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
 招标单位
@@ -92481,7 +92482,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E44" s="23" t="inlineStr">
+      <c r="E44" s="24" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $881万
@@ -92489,12 +92490,12 @@
 (26年-08月-12日)</t>
         </is>
       </c>
-      <c r="F44" s="22" t="inlineStr">
+      <c r="F44" s="23" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
 $871万
 $19,219/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="G44" s="20" t="inlineStr">
@@ -92520,7 +92521,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C45" s="24" t="inlineStr">
+      <c r="C45" s="23" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
 招标单位
@@ -92536,7 +92537,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E45" s="23" t="inlineStr">
+      <c r="E45" s="24" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $900万
@@ -92544,12 +92545,12 @@
 (26年-08月-11日)</t>
         </is>
       </c>
-      <c r="F45" s="22" t="inlineStr">
+      <c r="F45" s="23" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
 $869万
 $19,179/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="G45" s="20" t="inlineStr">
@@ -92591,7 +92592,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E46" s="23" t="inlineStr">
+      <c r="E46" s="24" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $897万
@@ -92599,12 +92600,12 @@
 (26年-08月-10日)</t>
         </is>
       </c>
-      <c r="F46" s="22" t="inlineStr">
+      <c r="F46" s="23" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
 $865万
 $19,104/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="G46" s="20" t="inlineStr">
@@ -92646,7 +92647,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E47" s="23" t="inlineStr">
+      <c r="E47" s="24" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $876万
@@ -92654,12 +92655,12 @@
 (26年-08月-14日)</t>
         </is>
       </c>
-      <c r="F47" s="22" t="inlineStr">
+      <c r="F47" s="23" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
 $864万
 $19,064/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="G47" s="20" t="inlineStr">
@@ -92701,7 +92702,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E48" s="23" t="inlineStr">
+      <c r="E48" s="24" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $895万
@@ -92709,12 +92710,12 @@
 (26年-08月-20日)</t>
         </is>
       </c>
-      <c r="F48" s="22" t="inlineStr">
+      <c r="F48" s="23" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
 $862万
 $19,029/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="G48" s="20" t="inlineStr">
@@ -92756,7 +92757,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E49" s="23" t="inlineStr">
+      <c r="E49" s="24" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $873万
@@ -92764,12 +92765,12 @@
 (26年-08月-18日)</t>
         </is>
       </c>
-      <c r="F49" s="22" t="inlineStr">
+      <c r="F49" s="23" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
 $860万
 $18,989/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="G49" s="20" t="inlineStr">
@@ -92811,7 +92812,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E50" s="23" t="inlineStr">
+      <c r="E50" s="24" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $873万
@@ -92819,12 +92820,12 @@
 (26年-08月-12日)</t>
         </is>
       </c>
-      <c r="F50" s="22" t="inlineStr">
+      <c r="F50" s="23" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
 $860万
 $18,989/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="G50" s="20" t="inlineStr">
@@ -92866,7 +92867,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E51" s="23" t="inlineStr">
+      <c r="E51" s="24" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $891万
@@ -92874,12 +92875,12 @@
 (26年-08月-11日)</t>
         </is>
       </c>
-      <c r="F51" s="22" t="inlineStr">
+      <c r="F51" s="23" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
 $857万
 $18,914/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="G51" s="20" t="inlineStr">
@@ -92921,7 +92922,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E52" s="23" t="inlineStr">
+      <c r="E52" s="24" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $869万
@@ -92929,12 +92930,12 @@
 (26年-08月-11日)</t>
         </is>
       </c>
-      <c r="F52" s="22" t="inlineStr">
+      <c r="F52" s="23" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
 $855万
 $18,876/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="G52" s="20" t="inlineStr">
@@ -92976,7 +92977,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E53" s="23" t="inlineStr">
+      <c r="E53" s="24" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $868万
@@ -92984,12 +92985,12 @@
 (26年-08月-14日)</t>
         </is>
       </c>
-      <c r="F53" s="22" t="inlineStr">
+      <c r="F53" s="23" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
 $853万
 $18,839/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="G53" s="20" t="inlineStr">
@@ -93031,7 +93032,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E54" s="23" t="inlineStr">
+      <c r="E54" s="24" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $866万
@@ -93039,12 +93040,12 @@
 (26年-08月-18日)</t>
         </is>
       </c>
-      <c r="F54" s="22" t="inlineStr">
+      <c r="F54" s="23" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
 $852万
 $18,799/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="G54" s="20" t="inlineStr">
@@ -93086,7 +93087,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E55" s="23" t="inlineStr">
+      <c r="E55" s="24" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $865万
@@ -93094,12 +93095,12 @@
 (26年-08月-12日)</t>
         </is>
       </c>
-      <c r="F55" s="22" t="inlineStr">
+      <c r="F55" s="23" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
 $850万
 $18,764/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="G55" s="20" t="inlineStr">
@@ -93141,7 +93142,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E56" s="23" t="inlineStr">
+      <c r="E56" s="24" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $864万
@@ -93149,12 +93150,12 @@
 (26年-08月-11日)</t>
         </is>
       </c>
-      <c r="F56" s="22" t="inlineStr">
+      <c r="F56" s="23" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
 $848万
 $18,724/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="G56" s="20" t="inlineStr">
@@ -93196,7 +93197,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E57" s="23" t="inlineStr">
+      <c r="E57" s="24" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $883万
@@ -93204,7 +93205,62 @@
 (26年-08月-10日)</t>
         </is>
       </c>
-      <c r="F57" s="22" t="inlineStr">
+      <c r="F57" s="23" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$847万
+$18,689/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G57" s="20" t="inlineStr">
+        <is>
+          <t>F | 453呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="58" customHeight="1">
+      <c r="A58" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B58" s="20" t="inlineStr">
+        <is>
+          <t>A | 775呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C58" s="20" t="inlineStr">
+        <is>
+          <t>B | 628呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D58" s="20" t="inlineStr">
+        <is>
+          <t>C | 449呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E58" s="24" t="inlineStr">
+        <is>
+          <t>D | 554呎 (2房)
+$887万
+$16,015/呎
+(26年-08月-22日)</t>
+        </is>
+      </c>
+      <c r="F58" s="22" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
 $847万
@@ -93212,61 +93268,6 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G57" s="20" t="inlineStr">
-        <is>
-          <t>F | 453呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="58" customHeight="1">
-      <c r="A58" s="19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B58" s="20" t="inlineStr">
-        <is>
-          <t>A | 775呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C58" s="20" t="inlineStr">
-        <is>
-          <t>B | 628呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D58" s="20" t="inlineStr">
-        <is>
-          <t>C | 449呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E58" s="23" t="inlineStr">
-        <is>
-          <t>D | 554呎 (2房)
-$887万
-$16,015/呎
-(26年-08月-22日)</t>
-        </is>
-      </c>
-      <c r="F58" s="22" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$847万
-$18,689/呎
-(已定价未售)</t>
-        </is>
-      </c>
       <c r="G58" s="20" t="inlineStr">
         <is>
           <t>F | 453呎 (2房)
@@ -93306,7 +93307,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E59" s="23" t="inlineStr">
+      <c r="E59" s="24" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $880万
@@ -93459,17 +93460,17 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>83</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>75</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -93569,7 +93570,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -93616,7 +93617,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="24" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -93663,7 +93664,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -93710,7 +93711,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -93757,7 +93758,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C10" s="24" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -93804,7 +93805,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C11" s="24" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -93851,7 +93852,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C12" s="24" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -93898,7 +93899,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C13" s="24" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -93945,7 +93946,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -93992,7 +93993,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C15" s="24" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94039,7 +94040,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C16" s="24" t="inlineStr">
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94086,7 +94087,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C17" s="24" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94133,7 +94134,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C18" s="24" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94180,7 +94181,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C19" s="24" t="inlineStr">
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94227,7 +94228,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C20" s="24" t="inlineStr">
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94274,7 +94275,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C21" s="24" t="inlineStr">
+      <c r="C21" s="23" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94282,15 +94283,15 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D21" s="22" t="inlineStr">
+      <c r="D21" s="23" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $929万
 $19,045/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E21" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $732万
@@ -94298,12 +94299,12 @@
 (26年-08月-20日)</t>
         </is>
       </c>
-      <c r="F21" s="22" t="inlineStr">
+      <c r="F21" s="23" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $885万
 $19,065/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -94321,7 +94322,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C22" s="24" t="inlineStr">
+      <c r="C22" s="23" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94329,28 +94330,28 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D22" s="22" t="inlineStr">
+      <c r="D22" s="23" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $928万
 $19,006/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E22" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E22" s="23" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $869万
 $19,521/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F22" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F22" s="23" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $883万
 $19,037/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -94368,7 +94369,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C23" s="24" t="inlineStr">
+      <c r="C23" s="23" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94376,28 +94377,28 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D23" s="22" t="inlineStr">
+      <c r="D23" s="23" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $926万
 $18,967/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E23" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E23" s="23" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $867万
 $19,492/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F23" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F23" s="23" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $882万
 $19,009/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -94415,7 +94416,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C24" s="24" t="inlineStr">
+      <c r="C24" s="23" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94423,28 +94424,28 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D24" s="22" t="inlineStr">
+      <c r="D24" s="23" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $926万
 $18,967/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E24" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E24" s="23" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $867万
 $19,492/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F24" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F24" s="23" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $882万
 $19,009/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -94462,7 +94463,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C25" s="24" t="inlineStr">
+      <c r="C25" s="23" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94470,28 +94471,28 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D25" s="22" t="inlineStr">
+      <c r="D25" s="23" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $922万
 $18,893/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E25" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E25" s="23" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $865万
 $19,434/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F25" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F25" s="23" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $879万
 $18,950/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -94509,7 +94510,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C26" s="24" t="inlineStr">
+      <c r="C26" s="23" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94517,28 +94518,28 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D26" s="22" t="inlineStr">
+      <c r="D26" s="23" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $920万
 $18,855/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E26" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E26" s="23" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $864万
 $19,404/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F26" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F26" s="23" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $878万
 $18,922/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -94556,7 +94557,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C27" s="24" t="inlineStr">
+      <c r="C27" s="23" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94564,23 +94565,23 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D27" s="22" t="inlineStr">
+      <c r="D27" s="23" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $918万
 $18,820/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E27" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E27" s="23" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $862万
 $19,375/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F27" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F27" s="24" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $745万
@@ -94603,7 +94604,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C28" s="24" t="inlineStr">
+      <c r="C28" s="23" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94611,23 +94612,23 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D28" s="22" t="inlineStr">
+      <c r="D28" s="23" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $916万
 $18,781/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E28" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E28" s="23" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $861万
 $19,346/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F28" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F28" s="24" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $744万
@@ -94650,7 +94651,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C29" s="24" t="inlineStr">
+      <c r="C29" s="23" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94658,28 +94659,28 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D29" s="22" t="inlineStr">
+      <c r="D29" s="23" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $915万
 $18,742/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E29" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E29" s="23" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $860万
 $19,317/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F29" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F29" s="23" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $874万
 $18,836/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -94697,7 +94698,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C30" s="24" t="inlineStr">
+      <c r="C30" s="23" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94705,28 +94706,28 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D30" s="22" t="inlineStr">
+      <c r="D30" s="23" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $913万
 $18,705/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E30" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E30" s="23" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $858万
 $19,290/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F30" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F30" s="23" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $873万
 $18,808/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -94744,7 +94745,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C31" s="24" t="inlineStr">
+      <c r="C31" s="23" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94752,28 +94753,28 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D31" s="22" t="inlineStr">
+      <c r="D31" s="23" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $911万
 $18,666/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E31" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E31" s="23" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $857万
 $19,261/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F31" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F31" s="24" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
-$871万
-$18,780/呎
-(已定价未售)</t>
+$741万
+$15,963/呎
+(26年-08月-26日)</t>
         </is>
       </c>
     </row>
@@ -94791,7 +94792,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C32" s="24" t="inlineStr">
+      <c r="C32" s="23" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94799,23 +94800,23 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D32" s="22" t="inlineStr">
+      <c r="D32" s="23" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $909万
 $18,631/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E32" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E32" s="23" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $856万
 $19,231/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F32" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F32" s="24" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $740万
@@ -94838,7 +94839,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C33" s="24" t="inlineStr">
+      <c r="C33" s="23" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94846,23 +94847,23 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D33" s="22" t="inlineStr">
+      <c r="D33" s="23" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $909万
 $18,631/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E33" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E33" s="23" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $856万
 $19,231/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F33" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F33" s="24" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $740万
@@ -94885,7 +94886,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C34" s="24" t="inlineStr">
+      <c r="C34" s="23" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94893,23 +94894,23 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D34" s="22" t="inlineStr">
+      <c r="D34" s="23" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $906万
 $18,555/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E34" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E34" s="23" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $853万
 $19,173/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F34" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F34" s="24" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $755万
@@ -94932,7 +94933,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C35" s="24" t="inlineStr">
+      <c r="C35" s="23" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94940,23 +94941,23 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D35" s="22" t="inlineStr">
+      <c r="D35" s="23" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $904万
 $18,520/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E35" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E35" s="23" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $852万
 $19,144/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F35" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F35" s="24" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $736万
@@ -94979,7 +94980,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C36" s="24" t="inlineStr">
+      <c r="C36" s="23" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94987,7 +94988,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D36" s="23" t="inlineStr">
+      <c r="D36" s="24" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $759万
@@ -94995,15 +94996,15 @@
 (26年-08月-19日)</t>
         </is>
       </c>
-      <c r="E36" s="22" t="inlineStr">
+      <c r="E36" s="23" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $851万
 $19,117/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F36" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F36" s="24" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $752万
@@ -95026,7 +95027,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C37" s="24" t="inlineStr">
+      <c r="C37" s="23" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -95034,7 +95035,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D37" s="23" t="inlineStr">
+      <c r="D37" s="24" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $758万
@@ -95042,15 +95043,15 @@
 (26年-08月-18日)</t>
         </is>
       </c>
-      <c r="E37" s="22" t="inlineStr">
+      <c r="E37" s="23" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $849万
 $19,088/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F37" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F37" s="24" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $727万
@@ -95073,7 +95074,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C38" s="24" t="inlineStr">
+      <c r="C38" s="23" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -95081,7 +95082,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D38" s="23" t="inlineStr">
+      <c r="D38" s="24" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $756万
@@ -95089,7 +95090,7 @@
 (26年-08月-18日)</t>
         </is>
       </c>
-      <c r="E38" s="23" t="inlineStr">
+      <c r="E38" s="24" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $714万
@@ -95097,7 +95098,7 @@
 (26年-08月-24日)</t>
         </is>
       </c>
-      <c r="F38" s="23" t="inlineStr">
+      <c r="F38" s="24" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $726万
@@ -95120,7 +95121,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C39" s="23" t="inlineStr">
+      <c r="C39" s="24" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 $1101万
@@ -95128,7 +95129,7 @@
 (26年-08月-17日)</t>
         </is>
       </c>
-      <c r="D39" s="23" t="inlineStr">
+      <c r="D39" s="24" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $754万
@@ -95136,7 +95137,7 @@
 (26年-08月-18日)</t>
         </is>
       </c>
-      <c r="E39" s="23" t="inlineStr">
+      <c r="E39" s="24" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $713万
@@ -95144,7 +95145,7 @@
 (26年-08月-24日)</t>
         </is>
       </c>
-      <c r="F39" s="23" t="inlineStr">
+      <c r="F39" s="24" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $725万
@@ -95167,7 +95168,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C40" s="23" t="inlineStr">
+      <c r="C40" s="24" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 $1099万
@@ -95175,7 +95176,7 @@
 (26年-08月-19日)</t>
         </is>
       </c>
-      <c r="D40" s="23" t="inlineStr">
+      <c r="D40" s="24" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $771万
@@ -95183,7 +95184,7 @@
 (26年-08月-19日)</t>
         </is>
       </c>
-      <c r="E40" s="23" t="inlineStr">
+      <c r="E40" s="24" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $712万
@@ -95191,7 +95192,7 @@
 (26年-08月-26日)</t>
         </is>
       </c>
-      <c r="F40" s="23" t="inlineStr">
+      <c r="F40" s="24" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $724万
@@ -95214,7 +95215,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C41" s="24" t="inlineStr">
+      <c r="C41" s="23" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -95222,7 +95223,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D41" s="23" t="inlineStr">
+      <c r="D41" s="24" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $751万
@@ -95230,7 +95231,7 @@
 (26年-08月-19日)</t>
         </is>
       </c>
-      <c r="E41" s="23" t="inlineStr">
+      <c r="E41" s="24" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $727万
@@ -95238,7 +95239,7 @@
 (26年-08月-23日)</t>
         </is>
       </c>
-      <c r="F41" s="23" t="inlineStr">
+      <c r="F41" s="24" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $722万
@@ -95261,7 +95262,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C42" s="24" t="inlineStr">
+      <c r="C42" s="23" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -95269,7 +95270,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D42" s="23" t="inlineStr">
+      <c r="D42" s="24" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $751万
@@ -95277,7 +95278,7 @@
 (26年-08月-19日)</t>
         </is>
       </c>
-      <c r="E42" s="23" t="inlineStr">
+      <c r="E42" s="24" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $711万
@@ -95285,7 +95286,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="F42" s="23" t="inlineStr">
+      <c r="F42" s="24" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $722万
@@ -95308,7 +95309,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C43" s="24" t="inlineStr">
+      <c r="C43" s="23" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -95316,7 +95317,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D43" s="23" t="inlineStr">
+      <c r="D43" s="24" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $749万
@@ -95324,7 +95325,7 @@
 (26年-08月-25日)</t>
         </is>
       </c>
-      <c r="E43" s="23" t="inlineStr">
+      <c r="E43" s="24" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $708万
@@ -95332,7 +95333,7 @@
 (26年-08月-23日)</t>
         </is>
       </c>
-      <c r="F43" s="23" t="inlineStr">
+      <c r="F43" s="24" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $720万
@@ -95355,7 +95356,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C44" s="24" t="inlineStr">
+      <c r="C44" s="23" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -95363,7 +95364,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D44" s="23" t="inlineStr">
+      <c r="D44" s="24" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $765万
@@ -95371,7 +95372,7 @@
 (26年-08月-20日)</t>
         </is>
       </c>
-      <c r="E44" s="23" t="inlineStr">
+      <c r="E44" s="24" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $707万
@@ -95379,7 +95380,7 @@
 (26年-08月-15日)</t>
         </is>
       </c>
-      <c r="F44" s="23" t="inlineStr">
+      <c r="F44" s="24" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $719万
@@ -95405,12 +95406,12 @@
       <c r="C45" s="24" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D45" s="23" t="inlineStr">
+$1116万
+$18,530/呎
+(26年-08月-26日)</t>
+        </is>
+      </c>
+      <c r="D45" s="24" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $746万
@@ -95418,7 +95419,7 @@
 (26年-08月-14日)</t>
         </is>
       </c>
-      <c r="E45" s="23" t="inlineStr">
+      <c r="E45" s="24" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $723万
@@ -95426,7 +95427,7 @@
 (26年-08月-21日)</t>
         </is>
       </c>
-      <c r="F45" s="23" t="inlineStr">
+      <c r="F45" s="24" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $718万
@@ -95449,7 +95450,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C46" s="24" t="inlineStr">
+      <c r="C46" s="23" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -95457,7 +95458,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D46" s="23" t="inlineStr">
+      <c r="D46" s="24" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $743万
@@ -95465,7 +95466,7 @@
 (26年-08月-18日)</t>
         </is>
       </c>
-      <c r="E46" s="23" t="inlineStr">
+      <c r="E46" s="24" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $721万
@@ -95473,7 +95474,7 @@
 (26年-08月-13日)</t>
         </is>
       </c>
-      <c r="F46" s="23" t="inlineStr">
+      <c r="F46" s="24" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $716万
@@ -95504,7 +95505,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D47" s="23" t="inlineStr">
+      <c r="D47" s="24" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $741万
@@ -95512,15 +95513,15 @@
 (26年-08月-11日)</t>
         </is>
       </c>
-      <c r="E47" s="23" t="inlineStr">
+      <c r="E47" s="24" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $703万
 $15,800/呎
-(26年-08月-10日)</t>
-        </is>
-      </c>
-      <c r="F47" s="23" t="inlineStr">
+(26年-08月-27日)</t>
+        </is>
+      </c>
+      <c r="F47" s="24" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $715万
@@ -95551,7 +95552,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D48" s="23" t="inlineStr">
+      <c r="D48" s="24" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $740万
@@ -95559,7 +95560,7 @@
 (26年-08月-19日)</t>
         </is>
       </c>
-      <c r="E48" s="23" t="inlineStr">
+      <c r="E48" s="24" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $719万
@@ -95567,7 +95568,7 @@
 (26年-08月-25日)</t>
         </is>
       </c>
-      <c r="F48" s="23" t="inlineStr">
+      <c r="F48" s="24" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $714万
@@ -95598,7 +95599,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D49" s="23" t="inlineStr">
+      <c r="D49" s="24" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $738万
@@ -95606,7 +95607,7 @@
 (26年-08月-20日)</t>
         </is>
       </c>
-      <c r="E49" s="23" t="inlineStr">
+      <c r="E49" s="24" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $717万
@@ -95614,7 +95615,7 @@
 (26年-08月-13日)</t>
         </is>
       </c>
-      <c r="F49" s="23" t="inlineStr">
+      <c r="F49" s="24" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $737万
@@ -95645,7 +95646,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D50" s="23" t="inlineStr">
+      <c r="D50" s="24" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $738万
@@ -95653,7 +95654,7 @@
 (26年-08月-19日)</t>
         </is>
       </c>
-      <c r="E50" s="23" t="inlineStr">
+      <c r="E50" s="24" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $701万
@@ -95661,7 +95662,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="F50" s="23" t="inlineStr">
+      <c r="F50" s="24" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $720万
@@ -95692,7 +95693,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D51" s="23" t="inlineStr">
+      <c r="D51" s="24" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $735万
@@ -95700,7 +95701,7 @@
 (26年-08月-10日)</t>
         </is>
       </c>
-      <c r="E51" s="23" t="inlineStr">
+      <c r="E51" s="24" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $715万
@@ -95708,7 +95709,7 @@
 (26年-08月-21日)</t>
         </is>
       </c>
-      <c r="F51" s="23" t="inlineStr">
+      <c r="F51" s="24" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $711万
@@ -95739,7 +95740,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D52" s="23" t="inlineStr">
+      <c r="D52" s="24" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $734万
@@ -95747,7 +95748,7 @@
 (26年-08月-12日)</t>
         </is>
       </c>
-      <c r="E52" s="23" t="inlineStr">
+      <c r="E52" s="24" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $698万
@@ -95755,7 +95756,7 @@
 (26年-08月-14日)</t>
         </is>
       </c>
-      <c r="F52" s="23" t="inlineStr">
+      <c r="F52" s="24" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $726万
@@ -95786,7 +95787,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D53" s="23" t="inlineStr">
+      <c r="D53" s="24" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $732万
@@ -95794,7 +95795,7 @@
 (26年-08月-19日)</t>
         </is>
       </c>
-      <c r="E53" s="23" t="inlineStr">
+      <c r="E53" s="24" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $713万
@@ -95802,7 +95803,7 @@
 (26年-08月-16日)</t>
         </is>
       </c>
-      <c r="F53" s="23" t="inlineStr">
+      <c r="F53" s="24" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $716万
@@ -95833,7 +95834,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D54" s="23" t="inlineStr">
+      <c r="D54" s="24" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $731万
@@ -95841,7 +95842,7 @@
 (26年-08月-11日)</t>
         </is>
       </c>
-      <c r="E54" s="23" t="inlineStr">
+      <c r="E54" s="24" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $712万
@@ -95849,12 +95850,12 @@
 (26年-08月-21日)</t>
         </is>
       </c>
-      <c r="F54" s="23" t="inlineStr">
+      <c r="F54" s="24" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $708万
 $15,249/呎
-(26年-08月-09日)</t>
+(26年-08月-27日)</t>
         </is>
       </c>
     </row>
@@ -95880,7 +95881,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D55" s="23" t="inlineStr">
+      <c r="D55" s="24" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $765万
@@ -95888,7 +95889,7 @@
 (26年-08月-14日)</t>
         </is>
       </c>
-      <c r="E55" s="23" t="inlineStr">
+      <c r="E55" s="24" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $711万
@@ -95896,7 +95897,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="F55" s="23" t="inlineStr">
+      <c r="F55" s="24" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $713万
@@ -95927,7 +95928,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D56" s="23" t="inlineStr">
+      <c r="D56" s="24" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $745万
@@ -95935,20 +95936,20 @@
 (26年-08月-14日)</t>
         </is>
       </c>
-      <c r="E56" s="22" t="inlineStr">
+      <c r="E56" s="23" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $824万
 $18,526/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F56" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F56" s="23" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $838万
 $18,062/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -95974,7 +95975,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D57" s="23" t="inlineStr">
+      <c r="D57" s="24" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $726万
@@ -95982,7 +95983,7 @@
 (26年-08月-11日)</t>
         </is>
       </c>
-      <c r="E57" s="23" t="inlineStr">
+      <c r="E57" s="24" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $709万
@@ -95990,12 +95991,12 @@
 (26年-08月-24日)</t>
         </is>
       </c>
-      <c r="F57" s="22" t="inlineStr">
+      <c r="F57" s="23" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $837万
 $18,034/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -96021,7 +96022,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D58" s="23" t="inlineStr">
+      <c r="D58" s="24" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $726万
@@ -96029,7 +96030,7 @@
 (26年-08月-26日)</t>
         </is>
       </c>
-      <c r="E58" s="23" t="inlineStr">
+      <c r="E58" s="24" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $709万
@@ -96037,12 +96038,12 @@
 (26年-08月-17日)</t>
         </is>
       </c>
-      <c r="F58" s="22" t="inlineStr">
+      <c r="F58" s="23" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $837万
 $18,034/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -96068,7 +96069,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D59" s="23" t="inlineStr">
+      <c r="D59" s="24" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $741万
@@ -96076,20 +96077,20 @@
 (26年-08月-17日)</t>
         </is>
       </c>
-      <c r="E59" s="22" t="inlineStr">
+      <c r="E59" s="23" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $821万
 $18,440/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F59" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F59" s="23" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $834万
 $17,983/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -96215,12 +96216,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>117</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -96230,7 +96231,7 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -96351,7 +96352,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -96359,7 +96360,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>C | 595呎 (2房)
 招标单位
@@ -96391,12 +96392,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H6" s="22" t="inlineStr">
+      <c r="H6" s="23" t="inlineStr">
         <is>
           <t>G | 459呎 (2房)
 $914万
 $19,911/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -96414,7 +96415,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="24" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -96422,7 +96423,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D7" s="24" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t>C | 595呎 (2房)
 招标单位
@@ -96454,12 +96455,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H7" s="22" t="inlineStr">
+      <c r="H7" s="23" t="inlineStr">
         <is>
           <t>G | 459呎 (2房)
 $912万
 $19,871/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -96477,7 +96478,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -96485,7 +96486,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D8" s="24" t="inlineStr">
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t>C | 595呎 (2房)
 招标单位
@@ -96517,12 +96518,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H8" s="22" t="inlineStr">
+      <c r="H8" s="23" t="inlineStr">
         <is>
           <t>G | 459呎 (2房)
 $904万
 $19,704/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -96540,7 +96541,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -96548,7 +96549,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D9" s="24" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t>C | 595呎 (2房)
 招标单位
@@ -96580,12 +96581,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H9" s="22" t="inlineStr">
+      <c r="H9" s="23" t="inlineStr">
         <is>
           <t>G | 459呎 (2房)
 $904万
 $19,704/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -96603,7 +96604,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C10" s="24" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -96611,7 +96612,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D10" s="24" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>C | 595呎 (2房)
 招标单位
@@ -96643,12 +96644,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H10" s="22" t="inlineStr">
+      <c r="H10" s="23" t="inlineStr">
         <is>
           <t>G | 459呎 (2房)
 $901万
 $19,625/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -96666,7 +96667,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C11" s="24" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -96674,7 +96675,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D11" s="24" t="inlineStr">
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t>C | 595呎 (2房)
 招标单位
@@ -96706,12 +96707,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H11" s="22" t="inlineStr">
+      <c r="H11" s="23" t="inlineStr">
         <is>
           <t>G | 459呎 (2房)
 $899万
 $19,584/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -96729,7 +96730,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C12" s="24" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -96737,7 +96738,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D12" s="24" t="inlineStr">
+      <c r="D12" s="23" t="inlineStr">
         <is>
           <t>C | 595呎 (2房)
 招标单位
@@ -96769,12 +96770,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H12" s="22" t="inlineStr">
+      <c r="H12" s="23" t="inlineStr">
         <is>
           <t>G | 459呎 (2房)
 $897万
 $19,547/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -96792,7 +96793,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C13" s="24" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -96800,7 +96801,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D13" s="24" t="inlineStr">
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t>C | 595呎 (2房)
 招标单位
@@ -96832,12 +96833,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H13" s="22" t="inlineStr">
+      <c r="H13" s="23" t="inlineStr">
         <is>
           <t>G | 459呎 (2房)
 $895万
 $19,508/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -96855,7 +96856,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -96863,7 +96864,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D14" s="24" t="inlineStr">
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t>C | 595呎 (2房)
 招标单位
@@ -96895,12 +96896,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H14" s="22" t="inlineStr">
+      <c r="H14" s="23" t="inlineStr">
         <is>
           <t>G | 459呎 (2房)
 $894万
 $19,468/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -96918,7 +96919,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C15" s="24" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -96926,7 +96927,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D15" s="24" t="inlineStr">
+      <c r="D15" s="23" t="inlineStr">
         <is>
           <t>C | 595呎 (2房)
 招标单位
@@ -96958,12 +96959,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H15" s="22" t="inlineStr">
+      <c r="H15" s="23" t="inlineStr">
         <is>
           <t>G | 459呎 (2房)
 $892万
 $19,431/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -96981,7 +96982,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C16" s="24" t="inlineStr">
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -96989,7 +96990,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D16" s="24" t="inlineStr">
+      <c r="D16" s="23" t="inlineStr">
         <is>
           <t>C | 595呎 (2房)
 招标单位
@@ -97021,12 +97022,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H16" s="22" t="inlineStr">
+      <c r="H16" s="23" t="inlineStr">
         <is>
           <t>G | 459呎 (2房)
 $890万
 $19,390/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -97044,7 +97045,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C17" s="24" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -97052,7 +97053,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D17" s="24" t="inlineStr">
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t>C | 595呎 (2房)
 招标单位
@@ -97084,12 +97085,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H17" s="22" t="inlineStr">
+      <c r="H17" s="23" t="inlineStr">
         <is>
           <t>G | 459呎 (2房)
 $888万
 $19,351/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -97107,7 +97108,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C18" s="24" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -97115,7 +97116,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D18" s="24" t="inlineStr">
+      <c r="D18" s="23" t="inlineStr">
         <is>
           <t>C | 595呎 (2房)
 招标单位
@@ -97147,12 +97148,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H18" s="22" t="inlineStr">
+      <c r="H18" s="23" t="inlineStr">
         <is>
           <t>G | 459呎 (2房)
 $886万
 $19,314/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -97170,7 +97171,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C19" s="24" t="inlineStr">
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -97178,7 +97179,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D19" s="24" t="inlineStr">
+      <c r="D19" s="23" t="inlineStr">
         <is>
           <t>C | 595呎 (2房)
 招标单位
@@ -97210,12 +97211,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H19" s="22" t="inlineStr">
+      <c r="H19" s="23" t="inlineStr">
         <is>
           <t>G | 459呎 (2房)
 $885万
 $19,275/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -97233,7 +97234,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C20" s="24" t="inlineStr">
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -97241,7 +97242,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D20" s="24" t="inlineStr">
+      <c r="D20" s="23" t="inlineStr">
         <is>
           <t>C | 595呎 (2房)
 招标单位
@@ -97273,12 +97274,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H20" s="22" t="inlineStr">
+      <c r="H20" s="23" t="inlineStr">
         <is>
           <t>G | 459呎 (2房)
 $883万
 $19,235/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -97296,7 +97297,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C21" s="24" t="inlineStr">
+      <c r="C21" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -97304,7 +97305,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D21" s="24" t="inlineStr">
+      <c r="D21" s="23" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -97336,7 +97337,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H21" s="23" t="inlineStr">
+      <c r="H21" s="24" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $743万
@@ -97359,7 +97360,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C22" s="24" t="inlineStr">
+      <c r="C22" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -97367,7 +97368,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D22" s="24" t="inlineStr">
+      <c r="D22" s="23" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -97399,7 +97400,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H22" s="23" t="inlineStr">
+      <c r="H22" s="24" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $725万
@@ -97422,7 +97423,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C23" s="24" t="inlineStr">
+      <c r="C23" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -97430,7 +97431,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D23" s="24" t="inlineStr">
+      <c r="D23" s="23" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -97462,7 +97463,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H23" s="23" t="inlineStr">
+      <c r="H23" s="24" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $741万
@@ -97485,7 +97486,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C24" s="23" t="inlineStr">
+      <c r="C24" s="24" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 $1537万
@@ -97493,7 +97494,7 @@
 (26年-08月-24日)</t>
         </is>
       </c>
-      <c r="D24" s="24" t="inlineStr">
+      <c r="D24" s="23" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -97525,7 +97526,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H24" s="23" t="inlineStr">
+      <c r="H24" s="24" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $724万
@@ -97548,7 +97549,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C25" s="24" t="inlineStr">
+      <c r="C25" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -97556,7 +97557,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D25" s="24" t="inlineStr">
+      <c r="D25" s="23" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -97588,7 +97589,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H25" s="23" t="inlineStr">
+      <c r="H25" s="24" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $722万
@@ -97611,7 +97612,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C26" s="24" t="inlineStr">
+      <c r="C26" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -97619,7 +97620,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D26" s="24" t="inlineStr">
+      <c r="D26" s="23" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -97651,7 +97652,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H26" s="23" t="inlineStr">
+      <c r="H26" s="24" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $721万
@@ -97674,7 +97675,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C27" s="24" t="inlineStr">
+      <c r="C27" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -97682,7 +97683,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D27" s="24" t="inlineStr">
+      <c r="D27" s="23" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -97714,7 +97715,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H27" s="23" t="inlineStr">
+      <c r="H27" s="24" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $720万
@@ -97737,7 +97738,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C28" s="24" t="inlineStr">
+      <c r="C28" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -97745,7 +97746,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D28" s="24" t="inlineStr">
+      <c r="D28" s="23" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -97777,7 +97778,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H28" s="23" t="inlineStr">
+      <c r="H28" s="24" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $718万
@@ -97800,7 +97801,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C29" s="24" t="inlineStr">
+      <c r="C29" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -97808,7 +97809,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D29" s="24" t="inlineStr">
+      <c r="D29" s="23" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -97840,7 +97841,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H29" s="23" t="inlineStr">
+      <c r="H29" s="24" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $717万
@@ -97863,7 +97864,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C30" s="24" t="inlineStr">
+      <c r="C30" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -97871,7 +97872,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D30" s="24" t="inlineStr">
+      <c r="D30" s="23" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -97895,15 +97896,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G30" s="22" t="inlineStr">
+      <c r="G30" s="23" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
 $714万
 $20,579/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H30" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="H30" s="24" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $716万
@@ -97926,7 +97927,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C31" s="24" t="inlineStr">
+      <c r="C31" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -97934,7 +97935,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D31" s="24" t="inlineStr">
+      <c r="D31" s="23" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -97958,15 +97959,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G31" s="22" t="inlineStr">
+      <c r="G31" s="23" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
 $713万
 $20,550/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H31" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="H31" s="24" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $715万
@@ -97989,7 +97990,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C32" s="24" t="inlineStr">
+      <c r="C32" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -97997,7 +97998,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D32" s="24" t="inlineStr">
+      <c r="D32" s="23" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -98021,15 +98022,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G32" s="22" t="inlineStr">
+      <c r="G32" s="23" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
 $712万
 $20,519/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H32" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="H32" s="24" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $714万
@@ -98052,7 +98053,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C33" s="24" t="inlineStr">
+      <c r="C33" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -98060,7 +98061,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D33" s="23" t="inlineStr">
+      <c r="D33" s="24" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 $1046万
@@ -98084,15 +98085,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G33" s="22" t="inlineStr">
+      <c r="G33" s="23" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
 $712万
 $20,519/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H33" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="H33" s="24" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $714万
@@ -98115,7 +98116,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C34" s="24" t="inlineStr">
+      <c r="C34" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -98123,7 +98124,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D34" s="24" t="inlineStr">
+      <c r="D34" s="23" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -98147,15 +98148,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G34" s="22" t="inlineStr">
+      <c r="G34" s="23" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
 $710万
 $20,458/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H34" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="H34" s="24" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $712万
@@ -98178,7 +98179,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C35" s="23" t="inlineStr">
+      <c r="C35" s="24" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 $1501万
@@ -98186,7 +98187,7 @@
 (26年-08月-20日)</t>
         </is>
       </c>
-      <c r="D35" s="24" t="inlineStr">
+      <c r="D35" s="23" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -98218,7 +98219,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H35" s="23" t="inlineStr">
+      <c r="H35" s="24" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $711万
@@ -98241,7 +98242,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C36" s="24" t="inlineStr">
+      <c r="C36" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -98249,7 +98250,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D36" s="24" t="inlineStr">
+      <c r="D36" s="23" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -98281,7 +98282,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H36" s="23" t="inlineStr">
+      <c r="H36" s="24" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $710万
@@ -98304,7 +98305,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C37" s="23" t="inlineStr">
+      <c r="C37" s="24" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 $1495万
@@ -98312,7 +98313,7 @@
 (26年-08月-19日)</t>
         </is>
       </c>
-      <c r="D37" s="23" t="inlineStr">
+      <c r="D37" s="24" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 $1036万
@@ -98344,7 +98345,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H37" s="23" t="inlineStr">
+      <c r="H37" s="24" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $709万
@@ -98367,7 +98368,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C38" s="23" t="inlineStr">
+      <c r="C38" s="24" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 $1492万
@@ -98375,7 +98376,7 @@
 (26年-08月-07日)</t>
         </is>
       </c>
-      <c r="D38" s="24" t="inlineStr">
+      <c r="D38" s="23" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -98407,7 +98408,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H38" s="23" t="inlineStr">
+      <c r="H38" s="24" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $708万
@@ -98430,7 +98431,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C39" s="23" t="inlineStr">
+      <c r="C39" s="24" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 $1489万
@@ -98438,7 +98439,7 @@
 (26年-08月-17日)</t>
         </is>
       </c>
-      <c r="D39" s="24" t="inlineStr">
+      <c r="D39" s="23" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -98470,7 +98471,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H39" s="23" t="inlineStr">
+      <c r="H39" s="24" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $706万
@@ -98493,7 +98494,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C40" s="23" t="inlineStr">
+      <c r="C40" s="24" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 $1486万
@@ -98501,7 +98502,7 @@
 (26年-08月-17日)</t>
         </is>
       </c>
-      <c r="D40" s="24" t="inlineStr">
+      <c r="D40" s="23" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -98525,15 +98526,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G40" s="22" t="inlineStr">
+      <c r="G40" s="23" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
 $704万
 $20,274/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H40" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="H40" s="24" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $722万
@@ -98556,7 +98557,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C41" s="23" t="inlineStr">
+      <c r="C41" s="24" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 $1483万
@@ -98564,7 +98565,7 @@
 (26年-08月-20日)</t>
         </is>
       </c>
-      <c r="D41" s="24" t="inlineStr">
+      <c r="D41" s="23" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -98588,15 +98589,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G41" s="22" t="inlineStr">
+      <c r="G41" s="23" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
 $702万
 $20,245/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H41" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="H41" s="24" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $704万
@@ -98619,7 +98620,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C42" s="23" t="inlineStr">
+      <c r="C42" s="24" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 $1483万
@@ -98627,7 +98628,7 @@
 (26年-08月-19日)</t>
         </is>
       </c>
-      <c r="D42" s="24" t="inlineStr">
+      <c r="D42" s="23" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -98651,15 +98652,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G42" s="22" t="inlineStr">
+      <c r="G42" s="23" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
 $702万
 $20,245/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H42" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="H42" s="24" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $704万
@@ -98682,7 +98683,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C43" s="23" t="inlineStr">
+      <c r="C43" s="24" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 $1477万
@@ -98690,7 +98691,7 @@
 (26年-08月-17日)</t>
         </is>
       </c>
-      <c r="D43" s="24" t="inlineStr">
+      <c r="D43" s="23" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -98714,15 +98715,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G43" s="22" t="inlineStr">
+      <c r="G43" s="23" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
 $700万
 $20,184/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H43" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="H43" s="24" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $719万
@@ -98745,7 +98746,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C44" s="23" t="inlineStr">
+      <c r="C44" s="24" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 $1474万
@@ -98753,7 +98754,7 @@
 (26年-08月-17日)</t>
         </is>
       </c>
-      <c r="D44" s="24" t="inlineStr">
+      <c r="D44" s="23" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -98777,15 +98778,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G44" s="22" t="inlineStr">
+      <c r="G44" s="23" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
 $699万
 $20,153/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H44" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="H44" s="24" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $718万
@@ -98808,7 +98809,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C45" s="23" t="inlineStr">
+      <c r="C45" s="24" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 $1471万
@@ -98816,7 +98817,7 @@
 (26年-08月-25日)</t>
         </is>
       </c>
-      <c r="D45" s="24" t="inlineStr">
+      <c r="D45" s="23" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -98840,15 +98841,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G45" s="22" t="inlineStr">
+      <c r="G45" s="23" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
 $698万
 $20,121/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H45" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="H45" s="24" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $717万
@@ -98871,7 +98872,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C46" s="24" t="inlineStr">
+      <c r="C46" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -98879,7 +98880,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D46" s="24" t="inlineStr">
+      <c r="D46" s="23" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -98903,15 +98904,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G46" s="22" t="inlineStr">
+      <c r="G46" s="23" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
 $696万
 $20,063/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H46" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="H46" s="24" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $714万
@@ -98934,7 +98935,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C47" s="24" t="inlineStr">
+      <c r="C47" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -98942,7 +98943,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D47" s="24" t="inlineStr">
+      <c r="D47" s="23" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -98966,15 +98967,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G47" s="22" t="inlineStr">
+      <c r="G47" s="23" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
 $695万
 $20,035/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H47" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="H47" s="24" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $697万
@@ -98997,7 +98998,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C48" s="24" t="inlineStr">
+      <c r="C48" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -99005,7 +99006,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D48" s="24" t="inlineStr">
+      <c r="D48" s="23" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -99029,15 +99030,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G48" s="22" t="inlineStr">
+      <c r="G48" s="23" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
 $694万
 $20,003/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H48" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="H48" s="24" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $696万
@@ -99060,7 +99061,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C49" s="24" t="inlineStr">
+      <c r="C49" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -99068,7 +99069,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D49" s="24" t="inlineStr">
+      <c r="D49" s="23" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -99092,15 +99093,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G49" s="22" t="inlineStr">
+      <c r="G49" s="23" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
 $693万
 $19,974/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H49" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="H49" s="24" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $695万
@@ -99123,7 +99124,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C50" s="24" t="inlineStr">
+      <c r="C50" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -99131,7 +99132,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D50" s="24" t="inlineStr">
+      <c r="D50" s="23" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -99155,7 +99156,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G50" s="23" t="inlineStr">
+      <c r="G50" s="24" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
 $583万
@@ -99163,7 +99164,7 @@
 (26年-08月-11日)</t>
         </is>
       </c>
-      <c r="H50" s="23" t="inlineStr">
+      <c r="H50" s="24" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $711万
@@ -99186,7 +99187,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C51" s="24" t="inlineStr">
+      <c r="C51" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -99194,7 +99195,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D51" s="24" t="inlineStr">
+      <c r="D51" s="23" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -99218,7 +99219,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G51" s="23" t="inlineStr">
+      <c r="G51" s="24" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
 $581万
@@ -99226,7 +99227,7 @@
 (26年-08月-10日)</t>
         </is>
       </c>
-      <c r="H51" s="23" t="inlineStr">
+      <c r="H51" s="24" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $709万
@@ -99249,7 +99250,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C52" s="24" t="inlineStr">
+      <c r="C52" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -99257,7 +99258,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D52" s="24" t="inlineStr">
+      <c r="D52" s="23" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -99281,7 +99282,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G52" s="23" t="inlineStr">
+      <c r="G52" s="24" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
 $581万
@@ -99289,7 +99290,7 @@
 (26年-08月-11日)</t>
         </is>
       </c>
-      <c r="H52" s="23" t="inlineStr">
+      <c r="H52" s="24" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $708万
@@ -99312,20 +99313,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C53" s="24" t="inlineStr">
+      <c r="C53" s="25" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
 -
-(在售)</t>
-        </is>
-      </c>
-      <c r="D53" s="24" t="inlineStr">
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D53" s="25" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="E53" s="20" t="inlineStr">
@@ -99344,7 +99345,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G53" s="23" t="inlineStr">
+      <c r="G53" s="24" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
 $580万
@@ -99352,7 +99353,7 @@
 (26年-08月-12日)</t>
         </is>
       </c>
-      <c r="H53" s="23" t="inlineStr">
+      <c r="H53" s="24" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $691万
@@ -99375,20 +99376,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C54" s="24" t="inlineStr">
+      <c r="C54" s="25" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
 -
-(在售)</t>
-        </is>
-      </c>
-      <c r="D54" s="24" t="inlineStr">
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D54" s="25" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="E54" s="20" t="inlineStr">
@@ -99407,7 +99408,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G54" s="23" t="inlineStr">
+      <c r="G54" s="24" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
 $579万
@@ -99415,7 +99416,7 @@
 (26年-08月-19日)</t>
         </is>
       </c>
-      <c r="H54" s="23" t="inlineStr">
+      <c r="H54" s="24" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $706万
@@ -99438,7 +99439,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C55" s="24" t="inlineStr">
+      <c r="C55" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -99446,7 +99447,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D55" s="24" t="inlineStr">
+      <c r="D55" s="23" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -99470,7 +99471,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G55" s="23" t="inlineStr">
+      <c r="G55" s="24" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
 $578万
@@ -99478,7 +99479,7 @@
 (26年-08月-24日)</t>
         </is>
       </c>
-      <c r="H55" s="23" t="inlineStr">
+      <c r="H55" s="24" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $689万
@@ -99501,7 +99502,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C56" s="24" t="inlineStr">
+      <c r="C56" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -99509,7 +99510,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D56" s="24" t="inlineStr">
+      <c r="D56" s="23" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -99533,7 +99534,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G56" s="23" t="inlineStr">
+      <c r="G56" s="24" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
 $577万
@@ -99541,7 +99542,7 @@
 (26年-08月-18日)</t>
         </is>
       </c>
-      <c r="H56" s="23" t="inlineStr">
+      <c r="H56" s="24" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $704万
@@ -99564,20 +99565,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C57" s="24" t="inlineStr">
+      <c r="C57" s="25" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
 -
-(在售)</t>
-        </is>
-      </c>
-      <c r="D57" s="24" t="inlineStr">
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D57" s="25" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="E57" s="20" t="inlineStr">
@@ -99596,7 +99597,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G57" s="23" t="inlineStr">
+      <c r="G57" s="24" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
 $576万
@@ -99604,7 +99605,7 @@
 (26年-08月-10日)</t>
         </is>
       </c>
-      <c r="H57" s="23" t="inlineStr">
+      <c r="H57" s="24" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $687万
@@ -99627,20 +99628,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C58" s="24" t="inlineStr">
+      <c r="C58" s="25" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
 -
-(在售)</t>
-        </is>
-      </c>
-      <c r="D58" s="24" t="inlineStr">
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D58" s="25" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="E58" s="20" t="inlineStr">
@@ -99659,15 +99660,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G58" s="22" t="inlineStr">
+      <c r="G58" s="23" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
 $685万
 $19,735/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H58" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="H58" s="24" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $687万
@@ -99690,20 +99691,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C59" s="24" t="inlineStr">
+      <c r="C59" s="25" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
 -
-(在售)</t>
-        </is>
-      </c>
-      <c r="D59" s="24" t="inlineStr">
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D59" s="25" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="E59" s="20" t="inlineStr">
@@ -99722,15 +99723,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G59" s="22" t="inlineStr">
+      <c r="G59" s="23" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
 $683万
 $19,674/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H59" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="H59" s="24" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $701万

--- a/web/files/九龙-将军澳-海瑅湾 II.xlsx
+++ b/web/files/九龙-将军澳-海瑅湾 II.xlsx
@@ -15268,7 +15268,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
@@ -31960,7 +31960,7 @@
       </c>
       <c r="G463" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H463" s="5" t="n">
@@ -54064,7 +54064,7 @@
       </c>
       <c r="G791" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H791" s="5" t="n">
@@ -55034,7 +55034,7 @@
       </c>
       <c r="G806" s="3" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H806" s="5" t="n">
@@ -55422,7 +55422,7 @@
       </c>
       <c r="G812" s="3" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H812" s="5" t="n">
@@ -55686,7 +55686,7 @@
       </c>
       <c r="G816" s="3" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H816" s="5" t="n">
@@ -56330,7 +56330,7 @@
       </c>
       <c r="G826" s="3" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H826" s="5" t="n">
@@ -56656,7 +56656,7 @@
       </c>
       <c r="G831" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H831" s="5" t="n">
@@ -57044,7 +57044,7 @@
       </c>
       <c r="G837" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H837" s="5" t="n">
@@ -59978,7 +59978,7 @@
       </c>
       <c r="G882" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H882" s="5" t="n">
@@ -85606,7 +85606,7 @@
       </c>
       <c r="G1260" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H1260" s="5" t="n">
@@ -89611,7 +89611,7 @@
           <t>E | 460呎 (2房)
 $733万
 $15,937/呎
-(26年-08月-09日)</t>
+(26年-08月-28日)</t>
         </is>
       </c>
     </row>
@@ -91992,7 +91992,7 @@
           <t>D | 554呎 (2房)
 $893万
 $16,116/呎
-(26年-08月-10日)</t>
+(26年-08月-28日)</t>
         </is>
       </c>
       <c r="F35" s="22" t="inlineStr">
@@ -95197,7 +95197,7 @@
           <t>E | 464呎 (2房)
 $724万
 $15,595/呎
-(26年-08月-10日)</t>
+(26年-08月-28日)</t>
         </is>
       </c>
     </row>
@@ -95338,7 +95338,7 @@
           <t>E | 464呎 (2房)
 $720万
 $15,523/呎
-(26年-08月-16日)</t>
+(26年-08月-28日)</t>
         </is>
       </c>
     </row>
@@ -95377,7 +95377,7 @@
           <t>D | 445呎 (2房)
 $707万
 $15,896/呎
-(26年-08月-15日)</t>
+(26年-08月-28日)</t>
         </is>
       </c>
       <c r="F44" s="24" t="inlineStr">
@@ -95432,7 +95432,7 @@
           <t>E | 464呎 (2房)
 $718万
 $15,478/呎
-(26年-08月-15日)</t>
+(26年-08月-28日)</t>
         </is>
       </c>
     </row>
@@ -95526,7 +95526,7 @@
           <t>E | 464呎 (2房)
 $715万
 $15,408/呎
-(26年-08月-16日)</t>
+(26年-08月-28日)</t>
         </is>
       </c>
     </row>
@@ -95573,7 +95573,7 @@
           <t>E | 464呎 (2房)
 $714万
 $15,386/呎
-(26年-08月-09日)</t>
+(26年-08月-28日)</t>
         </is>
       </c>
     </row>
@@ -95612,7 +95612,7 @@
           <t>D | 445呎 (2房)
 $717万
 $16,123/呎
-(26年-08月-13日)</t>
+(26年-08月-28日)</t>
         </is>
       </c>
       <c r="F49" s="24" t="inlineStr">
@@ -96035,7 +96035,7 @@
           <t>D | 445呎 (2房)
 $709万
 $15,932/呎
-(26年-08月-17日)</t>
+(26年-08月-28日)</t>
         </is>
       </c>
       <c r="F58" s="23" t="inlineStr">
@@ -99602,7 +99602,7 @@
           <t>F | 347呎 (1房)
 $576万
 $16,608/呎
-(26年-08月-10日)</t>
+(26年-08月-28日)</t>
         </is>
       </c>
       <c r="H57" s="24" t="inlineStr">

--- a/web/files/九龙-将军澳-海瑅湾 II.xlsx
+++ b/web/files/九龙-将军澳-海瑅湾 II.xlsx
@@ -11599,34 +11599,34 @@
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
-        <v>10221000</v>
+        <v>8892200</v>
       </c>
       <c r="I161" s="5" t="n">
-        <v>21655</v>
+        <v>18839</v>
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K161" s="5" t="n">
-        <v>8687850</v>
+        <v>8892200</v>
       </c>
       <c r="L161" s="5" t="n">
-        <v>18406</v>
+        <v>18839</v>
       </c>
       <c r="M161" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N161" s="3" t="inlineStr">
@@ -12267,23 +12267,23 @@
       </c>
       <c r="F171" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
-        <v>10180000</v>
+        <v>8653000</v>
       </c>
       <c r="I171" s="5" t="n">
-        <v>21568</v>
+        <v>18333</v>
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K171" s="5" t="n">
@@ -12294,7 +12294,7 @@
       </c>
       <c r="M171" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N171" s="3" t="inlineStr">
@@ -12329,34 +12329,34 @@
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
-        <v>8887000</v>
+        <v>7553900</v>
       </c>
       <c r="I172" s="5" t="n">
-        <v>19320</v>
+        <v>16422</v>
       </c>
       <c r="J172" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K172" s="5" t="n">
-        <v>7553950</v>
+        <v>7553900</v>
       </c>
       <c r="L172" s="5" t="n">
         <v>16422</v>
       </c>
       <c r="M172" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N172" s="3" t="inlineStr">
@@ -12981,34 +12981,34 @@
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
-        <v>8852000</v>
+        <v>7701200</v>
       </c>
       <c r="I182" s="5" t="n">
-        <v>19243</v>
+        <v>16742</v>
       </c>
       <c r="J182" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K182" s="5" t="n">
-        <v>7524200</v>
+        <v>7701200</v>
       </c>
       <c r="L182" s="5" t="n">
-        <v>16357</v>
+        <v>16742</v>
       </c>
       <c r="M182" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N182" s="3" t="inlineStr">
@@ -13307,34 +13307,34 @@
       </c>
       <c r="F187" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H187" s="5" t="n">
-        <v>8852000</v>
+        <v>7701200</v>
       </c>
       <c r="I187" s="5" t="n">
-        <v>19243</v>
+        <v>16742</v>
       </c>
       <c r="J187" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K187" s="5" t="n">
-        <v>7524200</v>
+        <v>7701200</v>
       </c>
       <c r="L187" s="5" t="n">
-        <v>16357</v>
+        <v>16742</v>
       </c>
       <c r="M187" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N187" s="3" t="inlineStr">
@@ -13571,34 +13571,34 @@
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
-        <v>10119000</v>
+        <v>8803500</v>
       </c>
       <c r="I191" s="5" t="n">
-        <v>21439</v>
+        <v>18651</v>
       </c>
       <c r="J191" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K191" s="5" t="n">
-        <v>8601150</v>
+        <v>8803500</v>
       </c>
       <c r="L191" s="5" t="n">
-        <v>18223</v>
+        <v>18651</v>
       </c>
       <c r="M191" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N191" s="3" t="inlineStr">
@@ -13633,34 +13633,34 @@
       </c>
       <c r="F192" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
-        <v>8816000</v>
+        <v>7669900</v>
       </c>
       <c r="I192" s="5" t="n">
-        <v>19165</v>
+        <v>16674</v>
       </c>
       <c r="J192" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K192" s="5" t="n">
-        <v>7493600</v>
+        <v>7669900</v>
       </c>
       <c r="L192" s="5" t="n">
-        <v>16290</v>
+        <v>16674</v>
       </c>
       <c r="M192" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N192" s="3" t="inlineStr">
@@ -14875,34 +14875,34 @@
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
-        <v>9999000</v>
+        <v>8499100</v>
       </c>
       <c r="I211" s="5" t="n">
-        <v>21184</v>
+        <v>18007</v>
       </c>
       <c r="J211" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K211" s="5" t="n">
-        <v>8499150</v>
+        <v>8499100</v>
       </c>
       <c r="L211" s="5" t="n">
         <v>18007</v>
       </c>
       <c r="M211" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N211" s="3" t="inlineStr">
@@ -15201,34 +15201,34 @@
       </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H216" s="5" t="n">
-        <v>9979000</v>
+        <v>8681700</v>
       </c>
       <c r="I216" s="5" t="n">
-        <v>21142</v>
+        <v>18393</v>
       </c>
       <c r="J216" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K216" s="5" t="n">
-        <v>8482150</v>
+        <v>8681700</v>
       </c>
       <c r="L216" s="5" t="n">
-        <v>17971</v>
+        <v>18393</v>
       </c>
       <c r="M216" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N216" s="3" t="inlineStr">
@@ -16179,34 +16179,34 @@
       </c>
       <c r="F231" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
-        <v>9939000</v>
+        <v>8448100</v>
       </c>
       <c r="I231" s="5" t="n">
-        <v>21057</v>
+        <v>17899</v>
       </c>
       <c r="J231" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K231" s="5" t="n">
-        <v>8448150</v>
+        <v>8448100</v>
       </c>
       <c r="L231" s="5" t="n">
         <v>17899</v>
       </c>
       <c r="M231" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N231" s="3" t="inlineStr">
@@ -16831,23 +16831,23 @@
       </c>
       <c r="F241" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H241" s="5" t="n">
-        <v>9880000</v>
+        <v>8398000</v>
       </c>
       <c r="I241" s="5" t="n">
-        <v>20932</v>
+        <v>17792</v>
       </c>
       <c r="J241" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K241" s="5" t="n">
@@ -16858,7 +16858,7 @@
       </c>
       <c r="M241" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N241" s="3" t="inlineStr">
@@ -17157,23 +17157,23 @@
       </c>
       <c r="F246" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H246" s="5" t="n">
-        <v>9860000</v>
+        <v>8381000</v>
       </c>
       <c r="I246" s="5" t="n">
-        <v>20890</v>
+        <v>17756</v>
       </c>
       <c r="J246" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K246" s="5" t="n">
@@ -17184,7 +17184,7 @@
       </c>
       <c r="M246" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N246" s="3" t="inlineStr">
@@ -17483,23 +17483,23 @@
       </c>
       <c r="F251" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
-        <v>9840000</v>
+        <v>8364000</v>
       </c>
       <c r="I251" s="5" t="n">
-        <v>20847</v>
+        <v>17720</v>
       </c>
       <c r="J251" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K251" s="5" t="n">
@@ -17510,7 +17510,7 @@
       </c>
       <c r="M251" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N251" s="3" t="inlineStr">
@@ -30339,34 +30339,34 @@
       </c>
       <c r="F439" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G439" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H439" s="5" t="n">
-        <v>10619000</v>
+        <v>9026100</v>
       </c>
       <c r="I439" s="5" t="n">
-        <v>19168</v>
+        <v>16293</v>
       </c>
       <c r="J439" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K439" s="5" t="n">
-        <v>9026150</v>
+        <v>9026100</v>
       </c>
       <c r="L439" s="5" t="n">
         <v>16293</v>
       </c>
       <c r="M439" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N439" s="3" t="inlineStr">
@@ -31551,23 +31551,23 @@
       </c>
       <c r="F457" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G457" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H457" s="5" t="n">
-        <v>10572000</v>
+        <v>8986200</v>
       </c>
       <c r="I457" s="5" t="n">
-        <v>19083</v>
+        <v>16221</v>
       </c>
       <c r="J457" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K457" s="5" t="n">
@@ -31578,7 +31578,7 @@
       </c>
       <c r="M457" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N457" s="3" t="inlineStr">
@@ -35125,23 +35125,23 @@
       </c>
       <c r="F510" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G510" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H510" s="5" t="n">
-        <v>8724000</v>
+        <v>7415400</v>
       </c>
       <c r="I510" s="5" t="n">
-        <v>19258</v>
+        <v>16370</v>
       </c>
       <c r="J510" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K510" s="5" t="n">
@@ -35152,7 +35152,7 @@
       </c>
       <c r="M510" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N510" s="3" t="inlineStr">
@@ -35529,34 +35529,34 @@
       </c>
       <c r="F516" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G516" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H516" s="5" t="n">
-        <v>8706000</v>
+        <v>7574200</v>
       </c>
       <c r="I516" s="5" t="n">
-        <v>19219</v>
+        <v>16720</v>
       </c>
       <c r="J516" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K516" s="5" t="n">
-        <v>7400100</v>
+        <v>7574200</v>
       </c>
       <c r="L516" s="5" t="n">
-        <v>16336</v>
+        <v>16720</v>
       </c>
       <c r="M516" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N516" s="3" t="inlineStr">
@@ -35933,34 +35933,34 @@
       </c>
       <c r="F522" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G522" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H522" s="5" t="n">
-        <v>8688000</v>
+        <v>7558500</v>
       </c>
       <c r="I522" s="5" t="n">
-        <v>19179</v>
+        <v>16685</v>
       </c>
       <c r="J522" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K522" s="5" t="n">
-        <v>7384800</v>
+        <v>7558500</v>
       </c>
       <c r="L522" s="5" t="n">
-        <v>16302</v>
+        <v>16685</v>
       </c>
       <c r="M522" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N522" s="3" t="inlineStr">
@@ -36337,34 +36337,34 @@
       </c>
       <c r="F528" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G528" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H528" s="5" t="n">
-        <v>8654000</v>
+        <v>7528900</v>
       </c>
       <c r="I528" s="5" t="n">
-        <v>19104</v>
+        <v>16620</v>
       </c>
       <c r="J528" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K528" s="5" t="n">
-        <v>7355900</v>
+        <v>7528900</v>
       </c>
       <c r="L528" s="5" t="n">
-        <v>16238</v>
+        <v>16620</v>
       </c>
       <c r="M528" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N528" s="3" t="inlineStr">
@@ -36741,34 +36741,34 @@
       </c>
       <c r="F534" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G534" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H534" s="5" t="n">
-        <v>8636000</v>
+        <v>7513300</v>
       </c>
       <c r="I534" s="5" t="n">
-        <v>19064</v>
+        <v>16586</v>
       </c>
       <c r="J534" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K534" s="5" t="n">
-        <v>7340600</v>
+        <v>7513300</v>
       </c>
       <c r="L534" s="5" t="n">
-        <v>16204</v>
+        <v>16586</v>
       </c>
       <c r="M534" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N534" s="3" t="inlineStr">
@@ -37145,34 +37145,34 @@
       </c>
       <c r="F540" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G540" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H540" s="5" t="n">
-        <v>8620000</v>
+        <v>7499400</v>
       </c>
       <c r="I540" s="5" t="n">
-        <v>19029</v>
+        <v>16555</v>
       </c>
       <c r="J540" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K540" s="5" t="n">
-        <v>7327000</v>
+        <v>7499400</v>
       </c>
       <c r="L540" s="5" t="n">
-        <v>16174</v>
+        <v>16555</v>
       </c>
       <c r="M540" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N540" s="3" t="inlineStr">
@@ -37549,34 +37549,34 @@
       </c>
       <c r="F546" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G546" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H546" s="5" t="n">
-        <v>8602000</v>
+        <v>7483700</v>
       </c>
       <c r="I546" s="5" t="n">
-        <v>18989</v>
+        <v>16520</v>
       </c>
       <c r="J546" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K546" s="5" t="n">
-        <v>7311700</v>
+        <v>7483700</v>
       </c>
       <c r="L546" s="5" t="n">
-        <v>16141</v>
+        <v>16520</v>
       </c>
       <c r="M546" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N546" s="3" t="inlineStr">
@@ -37953,34 +37953,34 @@
       </c>
       <c r="F552" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G552" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H552" s="5" t="n">
-        <v>8602000</v>
+        <v>7483700</v>
       </c>
       <c r="I552" s="5" t="n">
-        <v>18989</v>
+        <v>16520</v>
       </c>
       <c r="J552" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K552" s="5" t="n">
-        <v>7311700</v>
+        <v>7483700</v>
       </c>
       <c r="L552" s="5" t="n">
-        <v>16141</v>
+        <v>16520</v>
       </c>
       <c r="M552" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N552" s="3" t="inlineStr">
@@ -38357,34 +38357,34 @@
       </c>
       <c r="F558" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G558" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H558" s="5" t="n">
-        <v>8568000</v>
+        <v>7454100</v>
       </c>
       <c r="I558" s="5" t="n">
-        <v>18914</v>
+        <v>16455</v>
       </c>
       <c r="J558" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K558" s="5" t="n">
-        <v>7282800</v>
+        <v>7454100</v>
       </c>
       <c r="L558" s="5" t="n">
-        <v>16077</v>
+        <v>16455</v>
       </c>
       <c r="M558" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N558" s="3" t="inlineStr">
@@ -38761,34 +38761,34 @@
       </c>
       <c r="F564" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G564" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H564" s="5" t="n">
-        <v>8551000</v>
+        <v>7439300</v>
       </c>
       <c r="I564" s="5" t="n">
-        <v>18876</v>
+        <v>16422</v>
       </c>
       <c r="J564" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K564" s="5" t="n">
-        <v>7268350</v>
+        <v>7439300</v>
       </c>
       <c r="L564" s="5" t="n">
-        <v>16045</v>
+        <v>16422</v>
       </c>
       <c r="M564" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N564" s="3" t="inlineStr">
@@ -39165,34 +39165,34 @@
       </c>
       <c r="F570" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G570" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H570" s="5" t="n">
-        <v>8534000</v>
+        <v>7424500</v>
       </c>
       <c r="I570" s="5" t="n">
-        <v>18839</v>
+        <v>16390</v>
       </c>
       <c r="J570" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K570" s="5" t="n">
-        <v>7253900</v>
+        <v>7424500</v>
       </c>
       <c r="L570" s="5" t="n">
-        <v>16013</v>
+        <v>16390</v>
       </c>
       <c r="M570" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N570" s="3" t="inlineStr">
@@ -39569,34 +39569,34 @@
       </c>
       <c r="F576" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G576" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H576" s="5" t="n">
-        <v>8516000</v>
+        <v>7408900</v>
       </c>
       <c r="I576" s="5" t="n">
-        <v>18799</v>
+        <v>16355</v>
       </c>
       <c r="J576" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K576" s="5" t="n">
-        <v>7238600</v>
+        <v>7408900</v>
       </c>
       <c r="L576" s="5" t="n">
-        <v>15979</v>
+        <v>16355</v>
       </c>
       <c r="M576" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N576" s="3" t="inlineStr">
@@ -39973,34 +39973,34 @@
       </c>
       <c r="F582" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G582" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H582" s="5" t="n">
-        <v>8500000</v>
+        <v>7395000</v>
       </c>
       <c r="I582" s="5" t="n">
-        <v>18764</v>
+        <v>16325</v>
       </c>
       <c r="J582" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K582" s="5" t="n">
-        <v>7225000</v>
+        <v>7395000</v>
       </c>
       <c r="L582" s="5" t="n">
-        <v>15949</v>
+        <v>16325</v>
       </c>
       <c r="M582" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N582" s="3" t="inlineStr">
@@ -40377,23 +40377,23 @@
       </c>
       <c r="F588" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G588" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H588" s="5" t="n">
-        <v>8482000</v>
+        <v>7209700</v>
       </c>
       <c r="I588" s="5" t="n">
-        <v>18724</v>
+        <v>15915</v>
       </c>
       <c r="J588" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K588" s="5" t="n">
@@ -40404,7 +40404,7 @@
       </c>
       <c r="M588" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N588" s="3" t="inlineStr">
@@ -40781,34 +40781,34 @@
       </c>
       <c r="F594" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G594" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="H594" s="5" t="n">
-        <v>8466000</v>
+        <v>7365400</v>
       </c>
       <c r="I594" s="5" t="n">
-        <v>18689</v>
+        <v>16259</v>
       </c>
       <c r="J594" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K594" s="5" t="n">
-        <v>7196100</v>
+        <v>7365400</v>
       </c>
       <c r="L594" s="5" t="n">
-        <v>15885</v>
+        <v>16259</v>
       </c>
       <c r="M594" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N594" s="3" t="inlineStr">
@@ -50807,34 +50807,34 @@
       </c>
       <c r="F741" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G741" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H741" s="5" t="n">
-        <v>8727000</v>
+        <v>7592400</v>
       </c>
       <c r="I741" s="5" t="n">
-        <v>18808</v>
+        <v>16363</v>
       </c>
       <c r="J741" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K741" s="5" t="n">
-        <v>7417950</v>
+        <v>7592400</v>
       </c>
       <c r="L741" s="5" t="n">
-        <v>15987</v>
+        <v>16363</v>
       </c>
       <c r="M741" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N741" s="3" t="inlineStr">
@@ -51257,34 +51257,34 @@
       </c>
       <c r="F748" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G748" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H748" s="5" t="n">
-        <v>9109000</v>
+        <v>7742600</v>
       </c>
       <c r="I748" s="5" t="n">
-        <v>18666</v>
+        <v>15866</v>
       </c>
       <c r="J748" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K748" s="5" t="n">
-        <v>7742650</v>
+        <v>7742600</v>
       </c>
       <c r="L748" s="5" t="n">
         <v>15866</v>
       </c>
       <c r="M748" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N748" s="3" t="inlineStr">
@@ -51583,23 +51583,23 @@
       </c>
       <c r="F753" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G753" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H753" s="5" t="n">
-        <v>9092000</v>
+        <v>7728200</v>
       </c>
       <c r="I753" s="5" t="n">
-        <v>18631</v>
+        <v>15836</v>
       </c>
       <c r="J753" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K753" s="5" t="n">
@@ -51610,7 +51610,7 @@
       </c>
       <c r="M753" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N753" s="3" t="inlineStr">
@@ -52561,23 +52561,23 @@
       </c>
       <c r="F768" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G768" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H768" s="5" t="n">
-        <v>9038000</v>
+        <v>7682300</v>
       </c>
       <c r="I768" s="5" t="n">
-        <v>18520</v>
+        <v>15742</v>
       </c>
       <c r="J768" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K768" s="5" t="n">
@@ -52588,7 +52588,7 @@
       </c>
       <c r="M768" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N768" s="3" t="inlineStr">
@@ -52825,34 +52825,34 @@
       </c>
       <c r="F772" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G772" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="H772" s="5" t="n">
-        <v>8507000</v>
+        <v>7401000</v>
       </c>
       <c r="I772" s="5" t="n">
-        <v>19117</v>
+        <v>16631</v>
       </c>
       <c r="J772" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K772" s="5" t="n">
-        <v>7230950</v>
+        <v>7401000</v>
       </c>
       <c r="L772" s="5" t="n">
-        <v>16249</v>
+        <v>16631</v>
       </c>
       <c r="M772" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N772" s="3" t="inlineStr">
@@ -53151,34 +53151,34 @@
       </c>
       <c r="F777" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G777" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="H777" s="5" t="n">
-        <v>8494000</v>
+        <v>7389700</v>
       </c>
       <c r="I777" s="5" t="n">
-        <v>19088</v>
+        <v>16606</v>
       </c>
       <c r="J777" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K777" s="5" t="n">
-        <v>7219900</v>
+        <v>7389700</v>
       </c>
       <c r="L777" s="5" t="n">
-        <v>16224</v>
+        <v>16606</v>
       </c>
       <c r="M777" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N777" s="3" t="inlineStr">
@@ -59259,34 +59259,34 @@
       </c>
       <c r="F871" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G871" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H871" s="5" t="n">
-        <v>8381000</v>
+        <v>7123800</v>
       </c>
       <c r="I871" s="5" t="n">
-        <v>18062</v>
+        <v>15353</v>
       </c>
       <c r="J871" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K871" s="5" t="n">
-        <v>7123850</v>
+        <v>7123800</v>
       </c>
       <c r="L871" s="5" t="n">
         <v>15353</v>
       </c>
       <c r="M871" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N871" s="3" t="inlineStr">
@@ -59321,23 +59321,23 @@
       </c>
       <c r="F872" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G872" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="H872" s="5" t="n">
-        <v>8244000</v>
+        <v>7007400</v>
       </c>
       <c r="I872" s="5" t="n">
-        <v>18526</v>
+        <v>15747</v>
       </c>
       <c r="J872" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K872" s="5" t="n">
@@ -59348,7 +59348,7 @@
       </c>
       <c r="M872" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N872" s="3" t="inlineStr">
@@ -59585,23 +59585,23 @@
       </c>
       <c r="F876" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G876" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H876" s="5" t="n">
-        <v>8368000</v>
+        <v>7112800</v>
       </c>
       <c r="I876" s="5" t="n">
-        <v>18034</v>
+        <v>15329</v>
       </c>
       <c r="J876" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K876" s="5" t="n">
@@ -59612,7 +59612,7 @@
       </c>
       <c r="M876" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N876" s="3" t="inlineStr">
@@ -80861,23 +80861,23 @@
       </c>
       <c r="F1190" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G1190" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="H1190" s="5" t="n">
-        <v>6952000</v>
+        <v>5909200</v>
       </c>
       <c r="I1190" s="5" t="n">
-        <v>20035</v>
+        <v>17029</v>
       </c>
       <c r="J1190" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K1190" s="5" t="n">
@@ -80888,7 +80888,7 @@
       </c>
       <c r="M1190" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N1190" s="3" t="inlineStr">
@@ -81335,34 +81335,34 @@
       </c>
       <c r="F1197" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G1197" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H1197" s="5" t="n">
-        <v>6941000</v>
+        <v>5899800</v>
       </c>
       <c r="I1197" s="5" t="n">
-        <v>20003</v>
+        <v>17002</v>
       </c>
       <c r="J1197" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K1197" s="5" t="n">
-        <v>5899850</v>
+        <v>5899800</v>
       </c>
       <c r="L1197" s="5" t="n">
         <v>17002</v>
       </c>
       <c r="M1197" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N1197" s="3" t="inlineStr">
@@ -81809,34 +81809,34 @@
       </c>
       <c r="F1204" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G1204" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="H1204" s="5" t="n">
-        <v>6931000</v>
+        <v>5891300</v>
       </c>
       <c r="I1204" s="5" t="n">
-        <v>19974</v>
+        <v>16978</v>
       </c>
       <c r="J1204" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K1204" s="5" t="n">
-        <v>5891350</v>
+        <v>5891300</v>
       </c>
       <c r="L1204" s="5" t="n">
         <v>16978</v>
       </c>
       <c r="M1204" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N1204" s="3" t="inlineStr">
@@ -86549,34 +86549,34 @@
       </c>
       <c r="F1274" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G1274" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="H1274" s="5" t="n">
-        <v>6827000</v>
+        <v>5802900</v>
       </c>
       <c r="I1274" s="5" t="n">
-        <v>19674</v>
+        <v>16723</v>
       </c>
       <c r="J1274" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K1274" s="5" t="n">
-        <v>5802950</v>
+        <v>5802900</v>
       </c>
       <c r="L1274" s="5" t="n">
         <v>16723</v>
       </c>
       <c r="M1274" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N1274" s="3" t="inlineStr">
@@ -87498,7 +87498,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -87508,7 +87508,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -89010,12 +89010,12 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B36" s="23" t="inlineStr">
+      <c r="B36" s="24" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
-$1022万
-$21,655/呎
-(在售)</t>
+$889万
+$18,839/呎
+(26年-08月-28日)</t>
         </is>
       </c>
       <c r="C36" s="20" t="inlineStr">
@@ -89104,12 +89104,12 @@
           <t>32</t>
         </is>
       </c>
-      <c r="B38" s="23" t="inlineStr">
+      <c r="B38" s="24" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
-$1018万
-$21,568/呎
-(在售)</t>
+$865万
+$18,333/呎
+(26年-08月-28日)</t>
         </is>
       </c>
       <c r="C38" s="20" t="inlineStr">
@@ -89183,12 +89183,12 @@
 (26年-08月-11日)</t>
         </is>
       </c>
-      <c r="F39" s="23" t="inlineStr">
+      <c r="F39" s="24" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
-$889万
-$19,320/呎
-(在售)</t>
+$755万
+$16,422/呎
+(26年-08月-28日)</t>
         </is>
       </c>
     </row>
@@ -89277,12 +89277,12 @@
 (26年-08月-13日)</t>
         </is>
       </c>
-      <c r="F41" s="23" t="inlineStr">
+      <c r="F41" s="24" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
-$885万
-$19,243/呎
-(在售)</t>
+$770万
+$16,742/呎
+(26年-08月-28日)</t>
         </is>
       </c>
     </row>
@@ -89292,12 +89292,12 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B42" s="23" t="inlineStr">
+      <c r="B42" s="24" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
-$1012万
-$21,439/呎
-(在售)</t>
+$880万
+$18,651/呎
+(26年-08月-28日)</t>
         </is>
       </c>
       <c r="C42" s="20" t="inlineStr">
@@ -89324,12 +89324,12 @@
 (26年-08月-18日)</t>
         </is>
       </c>
-      <c r="F42" s="23" t="inlineStr">
+      <c r="F42" s="24" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
-$885万
-$19,243/呎
-(在售)</t>
+$770万
+$16,742/呎
+(26年-08月-28日)</t>
         </is>
       </c>
     </row>
@@ -89371,12 +89371,12 @@
 (26年-08月-14日)</t>
         </is>
       </c>
-      <c r="F43" s="23" t="inlineStr">
+      <c r="F43" s="24" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
-$882万
-$19,165/呎
-(在售)</t>
+$767万
+$16,674/呎
+(26年-08月-28日)</t>
         </is>
       </c>
     </row>
@@ -89480,12 +89480,12 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B46" s="23" t="inlineStr">
+      <c r="B46" s="24" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
-$1000万
-$21,184/呎
-(在售)</t>
+$850万
+$18,007/呎
+(26年-08月-28日)</t>
         </is>
       </c>
       <c r="C46" s="20" t="inlineStr">
@@ -89527,12 +89527,12 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B47" s="23" t="inlineStr">
+      <c r="B47" s="24" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
-$998万
-$21,142/呎
-(在售)</t>
+$868万
+$18,393/呎
+(26年-08月-28日)</t>
         </is>
       </c>
       <c r="C47" s="20" t="inlineStr">
@@ -89668,12 +89668,12 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B50" s="23" t="inlineStr">
+      <c r="B50" s="24" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
-$994万
-$21,057/呎
-(在售)</t>
+$845万
+$17,899/呎
+(26年-08月-28日)</t>
         </is>
       </c>
       <c r="C50" s="20" t="inlineStr">
@@ -89762,12 +89762,12 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B52" s="23" t="inlineStr">
+      <c r="B52" s="24" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
-$988万
-$20,932/呎
-(在售)</t>
+$840万
+$17,792/呎
+(26年-08月-28日)</t>
         </is>
       </c>
       <c r="C52" s="20" t="inlineStr">
@@ -89809,12 +89809,12 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B53" s="23" t="inlineStr">
+      <c r="B53" s="24" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
-$986万
-$20,890/呎
-(在售)</t>
+$838万
+$17,756/呎
+(26年-08月-28日)</t>
         </is>
       </c>
       <c r="C53" s="20" t="inlineStr">
@@ -89856,12 +89856,12 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B54" s="23" t="inlineStr">
+      <c r="B54" s="24" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
-$984万
-$20,847/呎
-(在售)</t>
+$836万
+$17,720/呎
+(26年-08月-28日)</t>
         </is>
       </c>
       <c r="C54" s="20" t="inlineStr">
@@ -90253,7 +90253,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -90263,7 +90263,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>44</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -91767,12 +91767,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E31" s="23" t="inlineStr">
+      <c r="E31" s="24" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
-$1062万
-$19,168/呎
-(在售)</t>
+$903万
+$16,293/呎
+(26年-08月-28日)</t>
         </is>
       </c>
       <c r="F31" s="22" t="inlineStr">
@@ -91932,12 +91932,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E34" s="23" t="inlineStr">
+      <c r="E34" s="24" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
-$1057万
-$19,083/呎
-(在售)</t>
+$899万
+$16,221/呎
+(26年-08月-27日)</t>
         </is>
       </c>
       <c r="F34" s="22" t="inlineStr">
@@ -92435,12 +92435,12 @@
 (26年-08月-14日)</t>
         </is>
       </c>
-      <c r="F43" s="23" t="inlineStr">
+      <c r="F43" s="24" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
-$872万
-$19,258/呎
-(在售)</t>
+$742万
+$16,370/呎
+(26年-08月-28日)</t>
         </is>
       </c>
       <c r="G43" s="20" t="inlineStr">
@@ -92490,12 +92490,12 @@
 (26年-08月-12日)</t>
         </is>
       </c>
-      <c r="F44" s="23" t="inlineStr">
+      <c r="F44" s="24" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
-$871万
-$19,219/呎
-(在售)</t>
+$757万
+$16,720/呎
+(26年-08月-28日)</t>
         </is>
       </c>
       <c r="G44" s="20" t="inlineStr">
@@ -92545,12 +92545,12 @@
 (26年-08月-11日)</t>
         </is>
       </c>
-      <c r="F45" s="23" t="inlineStr">
+      <c r="F45" s="24" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
-$869万
-$19,179/呎
-(在售)</t>
+$756万
+$16,685/呎
+(26年-08月-28日)</t>
         </is>
       </c>
       <c r="G45" s="20" t="inlineStr">
@@ -92600,12 +92600,12 @@
 (26年-08月-10日)</t>
         </is>
       </c>
-      <c r="F46" s="23" t="inlineStr">
+      <c r="F46" s="24" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
-$865万
-$19,104/呎
-(在售)</t>
+$753万
+$16,620/呎
+(26年-08月-28日)</t>
         </is>
       </c>
       <c r="G46" s="20" t="inlineStr">
@@ -92655,12 +92655,12 @@
 (26年-08月-14日)</t>
         </is>
       </c>
-      <c r="F47" s="23" t="inlineStr">
+      <c r="F47" s="24" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
-$864万
-$19,064/呎
-(在售)</t>
+$751万
+$16,586/呎
+(26年-08月-28日)</t>
         </is>
       </c>
       <c r="G47" s="20" t="inlineStr">
@@ -92710,12 +92710,12 @@
 (26年-08月-20日)</t>
         </is>
       </c>
-      <c r="F48" s="23" t="inlineStr">
+      <c r="F48" s="24" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
-$862万
-$19,029/呎
-(在售)</t>
+$750万
+$16,555/呎
+(26年-08月-28日)</t>
         </is>
       </c>
       <c r="G48" s="20" t="inlineStr">
@@ -92765,12 +92765,12 @@
 (26年-08月-18日)</t>
         </is>
       </c>
-      <c r="F49" s="23" t="inlineStr">
+      <c r="F49" s="24" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
-$860万
-$18,989/呎
-(在售)</t>
+$748万
+$16,520/呎
+(26年-08月-28日)</t>
         </is>
       </c>
       <c r="G49" s="20" t="inlineStr">
@@ -92820,12 +92820,12 @@
 (26年-08月-12日)</t>
         </is>
       </c>
-      <c r="F50" s="23" t="inlineStr">
+      <c r="F50" s="24" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
-$860万
-$18,989/呎
-(在售)</t>
+$748万
+$16,520/呎
+(26年-08月-28日)</t>
         </is>
       </c>
       <c r="G50" s="20" t="inlineStr">
@@ -92875,12 +92875,12 @@
 (26年-08月-11日)</t>
         </is>
       </c>
-      <c r="F51" s="23" t="inlineStr">
+      <c r="F51" s="24" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
-$857万
-$18,914/呎
-(在售)</t>
+$745万
+$16,455/呎
+(26年-08月-28日)</t>
         </is>
       </c>
       <c r="G51" s="20" t="inlineStr">
@@ -92930,12 +92930,12 @@
 (26年-08月-11日)</t>
         </is>
       </c>
-      <c r="F52" s="23" t="inlineStr">
+      <c r="F52" s="24" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
-$855万
-$18,876/呎
-(在售)</t>
+$744万
+$16,422/呎
+(26年-08月-28日)</t>
         </is>
       </c>
       <c r="G52" s="20" t="inlineStr">
@@ -92985,12 +92985,12 @@
 (26年-08月-14日)</t>
         </is>
       </c>
-      <c r="F53" s="23" t="inlineStr">
+      <c r="F53" s="24" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
-$853万
-$18,839/呎
-(在售)</t>
+$742万
+$16,390/呎
+(26年-08月-28日)</t>
         </is>
       </c>
       <c r="G53" s="20" t="inlineStr">
@@ -93040,12 +93040,12 @@
 (26年-08月-18日)</t>
         </is>
       </c>
-      <c r="F54" s="23" t="inlineStr">
+      <c r="F54" s="24" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
-$852万
-$18,799/呎
-(在售)</t>
+$741万
+$16,355/呎
+(26年-08月-28日)</t>
         </is>
       </c>
       <c r="G54" s="20" t="inlineStr">
@@ -93095,12 +93095,12 @@
 (26年-08月-12日)</t>
         </is>
       </c>
-      <c r="F55" s="23" t="inlineStr">
+      <c r="F55" s="24" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
-$850万
-$18,764/呎
-(在售)</t>
+$740万
+$16,325/呎
+(26年-08月-28日)</t>
         </is>
       </c>
       <c r="G55" s="20" t="inlineStr">
@@ -93150,12 +93150,12 @@
 (26年-08月-11日)</t>
         </is>
       </c>
-      <c r="F56" s="23" t="inlineStr">
+      <c r="F56" s="24" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
-$848万
-$18,724/呎
-(在售)</t>
+$721万
+$15,915/呎
+(26年-08月-28日)</t>
         </is>
       </c>
       <c r="G56" s="20" t="inlineStr">
@@ -93205,12 +93205,12 @@
 (26年-08月-10日)</t>
         </is>
       </c>
-      <c r="F57" s="23" t="inlineStr">
+      <c r="F57" s="24" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
-$847万
-$18,689/呎
-(在售)</t>
+$737万
+$16,259/呎
+(26年-08月-29日)</t>
         </is>
       </c>
       <c r="G57" s="20" t="inlineStr">
@@ -93460,7 +93460,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>74</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -93470,7 +93470,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>84</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -94722,12 +94722,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F30" s="23" t="inlineStr">
+      <c r="F30" s="24" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
-$873万
-$18,808/呎
-(在售)</t>
+$759万
+$16,363/呎
+(26年-08月-27日)</t>
         </is>
       </c>
     </row>
@@ -94753,12 +94753,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D31" s="23" t="inlineStr">
+      <c r="D31" s="24" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
-$911万
-$18,666/呎
-(在售)</t>
+$774万
+$15,866/呎
+(26年-08月-28日)</t>
         </is>
       </c>
       <c r="E31" s="23" t="inlineStr">
@@ -94800,7 +94800,54 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D32" s="23" t="inlineStr">
+      <c r="D32" s="24" t="inlineStr">
+        <is>
+          <t>C | 488呎 (2房)
+$773万
+$15,836/呎
+(26年-08月-28日)</t>
+        </is>
+      </c>
+      <c r="E32" s="23" t="inlineStr">
+        <is>
+          <t>D | 445呎 (2房)
+$856万
+$19,231/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F32" s="24" t="inlineStr">
+        <is>
+          <t>E | 464呎 (2房)
+$740万
+$15,939/呎
+(26年-08月-23日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="inlineStr">
+        <is>
+          <t>A | 472呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C33" s="23" t="inlineStr">
+        <is>
+          <t>B | 602呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D33" s="23" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $909万
@@ -94808,7 +94855,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E32" s="23" t="inlineStr">
+      <c r="E33" s="23" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $856万
@@ -94816,53 +94863,6 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F32" s="24" t="inlineStr">
-        <is>
-          <t>E | 464呎 (2房)
-$740万
-$15,939/呎
-(26年-08月-23日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="58" customHeight="1">
-      <c r="A33" s="19" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B33" s="20" t="inlineStr">
-        <is>
-          <t>A | 472呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C33" s="23" t="inlineStr">
-        <is>
-          <t>B | 602呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D33" s="23" t="inlineStr">
-        <is>
-          <t>C | 488呎 (2房)
-$909万
-$18,631/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E33" s="23" t="inlineStr">
-        <is>
-          <t>D | 445呎 (2房)
-$856万
-$19,231/呎
-(在售)</t>
-        </is>
-      </c>
       <c r="F33" s="24" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
@@ -94941,12 +94941,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D35" s="23" t="inlineStr">
+      <c r="D35" s="24" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
-$904万
-$18,520/呎
-(在售)</t>
+$768万
+$15,742/呎
+(26年-08月-28日)</t>
         </is>
       </c>
       <c r="E35" s="23" t="inlineStr">
@@ -94996,12 +94996,12 @@
 (26年-08月-19日)</t>
         </is>
       </c>
-      <c r="E36" s="23" t="inlineStr">
+      <c r="E36" s="24" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
-$851万
-$19,117/呎
-(在售)</t>
+$740万
+$16,631/呎
+(26年-08月-29日)</t>
         </is>
       </c>
       <c r="F36" s="24" t="inlineStr">
@@ -95043,12 +95043,12 @@
 (26年-08月-18日)</t>
         </is>
       </c>
-      <c r="E37" s="23" t="inlineStr">
+      <c r="E37" s="24" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
-$849万
-$19,088/呎
-(在售)</t>
+$739万
+$16,606/呎
+(26年-08月-29日)</t>
         </is>
       </c>
       <c r="F37" s="24" t="inlineStr">
@@ -95936,20 +95936,20 @@
 (26年-08月-14日)</t>
         </is>
       </c>
-      <c r="E56" s="23" t="inlineStr">
+      <c r="E56" s="24" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
-$824万
-$18,526/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F56" s="23" t="inlineStr">
+$701万
+$15,747/呎
+(26年-08月-29日)</t>
+        </is>
+      </c>
+      <c r="F56" s="24" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
-$838万
-$18,062/呎
-(在售)</t>
+$712万
+$15,353/呎
+(26年-08月-27日)</t>
         </is>
       </c>
     </row>
@@ -95991,12 +95991,12 @@
 (26年-08月-24日)</t>
         </is>
       </c>
-      <c r="F57" s="23" t="inlineStr">
+      <c r="F57" s="24" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
-$837万
-$18,034/呎
-(在售)</t>
+$711万
+$15,329/呎
+(26年-08月-27日)</t>
         </is>
       </c>
     </row>
@@ -96216,7 +96216,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>113</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -96226,7 +96226,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -98967,12 +98967,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G47" s="23" t="inlineStr">
+      <c r="G47" s="24" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
-$695万
-$20,035/呎
-(在售)</t>
+$591万
+$17,029/呎
+(26年-08月-29日)</t>
         </is>
       </c>
       <c r="H47" s="24" t="inlineStr">
@@ -99030,12 +99030,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G48" s="23" t="inlineStr">
+      <c r="G48" s="24" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
-$694万
-$20,003/呎
-(在售)</t>
+$590万
+$17,002/呎
+(26年-08月-28日)</t>
         </is>
       </c>
       <c r="H48" s="24" t="inlineStr">
@@ -99093,12 +99093,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G49" s="23" t="inlineStr">
+      <c r="G49" s="24" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
-$693万
-$19,974/呎
-(在售)</t>
+$589万
+$16,978/呎
+(26年-08月-29日)</t>
         </is>
       </c>
       <c r="H49" s="24" t="inlineStr">
@@ -99723,12 +99723,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G59" s="23" t="inlineStr">
+      <c r="G59" s="24" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
-$683万
-$19,674/呎
-(在售)</t>
+$580万
+$16,723/呎
+(26年-08月-29日)</t>
         </is>
       </c>
       <c r="H59" s="24" t="inlineStr">

--- a/web/files/九龙-将军澳-海瑅湾 II.xlsx
+++ b/web/files/九龙-将军澳-海瑅湾 II.xlsx
@@ -9398,7 +9398,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -12655,34 +12655,34 @@
       </c>
       <c r="F177" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
-        <v>8869000</v>
+        <v>7538600</v>
       </c>
       <c r="I177" s="5" t="n">
-        <v>19280</v>
+        <v>16388</v>
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K177" s="5" t="n">
-        <v>7538650</v>
+        <v>7538600</v>
       </c>
       <c r="L177" s="5" t="n">
         <v>16388</v>
       </c>
       <c r="M177" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N177" s="3" t="inlineStr">
@@ -13897,34 +13897,34 @@
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
-        <v>10079000</v>
+        <v>8567100</v>
       </c>
       <c r="I196" s="5" t="n">
-        <v>21354</v>
+        <v>18151</v>
       </c>
       <c r="J196" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K196" s="5" t="n">
-        <v>8567150</v>
+        <v>8567100</v>
       </c>
       <c r="L196" s="5" t="n">
         <v>18151</v>
       </c>
       <c r="M196" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N196" s="3" t="inlineStr">
@@ -15527,34 +15527,34 @@
       </c>
       <c r="F221" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H221" s="5" t="n">
-        <v>9959000</v>
+        <v>8465100</v>
       </c>
       <c r="I221" s="5" t="n">
-        <v>21100</v>
+        <v>17935</v>
       </c>
       <c r="J221" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K221" s="5" t="n">
-        <v>8465150</v>
+        <v>8465100</v>
       </c>
       <c r="L221" s="5" t="n">
         <v>17935</v>
       </c>
       <c r="M221" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N221" s="3" t="inlineStr">
@@ -18935,34 +18935,34 @@
       </c>
       <c r="F273" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="H273" s="5" t="n">
-        <v>8225000</v>
+        <v>6991200</v>
       </c>
       <c r="I273" s="5" t="n">
-        <v>18442</v>
+        <v>15675</v>
       </c>
       <c r="J273" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K273" s="5" t="n">
-        <v>6991250</v>
+        <v>6991200</v>
       </c>
       <c r="L273" s="5" t="n">
         <v>15675</v>
       </c>
       <c r="M273" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N273" s="3" t="inlineStr">
@@ -32491,38 +32491,30 @@
       </c>
       <c r="F471" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G471" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H471" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I471" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="H471" s="5" t="n">
+        <v>12545000</v>
+      </c>
+      <c r="I471" s="5" t="n">
+        <v>19976</v>
       </c>
       <c r="J471" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K471" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L471" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K471" s="5" t="n">
+        <v>12545000</v>
+      </c>
+      <c r="L471" s="5" t="n">
+        <v>19976</v>
       </c>
       <c r="M471" s="3" t="inlineStr">
         <is>
@@ -32531,7 +32523,7 @@
       </c>
       <c r="N471" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -51847,23 +51839,23 @@
       </c>
       <c r="F757" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G757" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H757" s="5" t="n">
-        <v>8558000</v>
+        <v>7274300</v>
       </c>
       <c r="I757" s="5" t="n">
-        <v>19231</v>
+        <v>16347</v>
       </c>
       <c r="J757" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K757" s="5" t="n">
@@ -51874,7 +51866,7 @@
       </c>
       <c r="M757" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N757" s="3" t="inlineStr">
@@ -52235,34 +52227,34 @@
       </c>
       <c r="F763" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G763" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H763" s="5" t="n">
-        <v>9055000</v>
+        <v>7877800</v>
       </c>
       <c r="I763" s="5" t="n">
-        <v>18555</v>
+        <v>16143</v>
       </c>
       <c r="J763" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K763" s="5" t="n">
-        <v>7696750</v>
+        <v>7877800</v>
       </c>
       <c r="L763" s="5" t="n">
-        <v>15772</v>
+        <v>16143</v>
       </c>
       <c r="M763" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N763" s="3" t="inlineStr">
@@ -52499,34 +52491,34 @@
       </c>
       <c r="F767" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G767" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="H767" s="5" t="n">
-        <v>8519000</v>
+        <v>7241100</v>
       </c>
       <c r="I767" s="5" t="n">
-        <v>19144</v>
+        <v>16272</v>
       </c>
       <c r="J767" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K767" s="5" t="n">
-        <v>7241150</v>
+        <v>7241100</v>
       </c>
       <c r="L767" s="5" t="n">
         <v>16272</v>
       </c>
       <c r="M767" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N767" s="3" t="inlineStr">
@@ -55541,38 +55533,30 @@
       </c>
       <c r="F814" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G814" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H814" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I814" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="H814" s="5" t="n">
+        <v>10905000</v>
+      </c>
+      <c r="I814" s="5" t="n">
+        <v>18115</v>
       </c>
       <c r="J814" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K814" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L814" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K814" s="5" t="n">
+        <v>10905000</v>
+      </c>
+      <c r="L814" s="5" t="n">
+        <v>18115</v>
       </c>
       <c r="M814" s="3" t="inlineStr">
         <is>
@@ -55581,7 +55565,7 @@
       </c>
       <c r="N814" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -59066,10 +59050,10 @@
         </is>
       </c>
       <c r="H868" s="5" t="n">
-        <v>7646600</v>
+        <v>7464600</v>
       </c>
       <c r="I868" s="5" t="n">
-        <v>15669</v>
+        <v>15296</v>
       </c>
       <c r="J868" s="3" t="inlineStr">
         <is>
@@ -59077,10 +59061,10 @@
         </is>
       </c>
       <c r="K868" s="5" t="n">
-        <v>7646600</v>
+        <v>7464600</v>
       </c>
       <c r="L868" s="5" t="n">
-        <v>15669</v>
+        <v>15296</v>
       </c>
       <c r="M868" s="3" t="inlineStr">
         <is>
@@ -60299,34 +60283,34 @@
       </c>
       <c r="F887" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G887" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H887" s="5" t="n">
-        <v>8206000</v>
+        <v>7139200</v>
       </c>
       <c r="I887" s="5" t="n">
-        <v>18440</v>
+        <v>16043</v>
       </c>
       <c r="J887" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K887" s="5" t="n">
-        <v>6975100</v>
+        <v>7139200</v>
       </c>
       <c r="L887" s="5" t="n">
-        <v>15674</v>
+        <v>16043</v>
       </c>
       <c r="M887" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N887" s="3" t="inlineStr">
@@ -75999,38 +75983,30 @@
       </c>
       <c r="F1117" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G1117" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H1117" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I1117" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="H1117" s="5" t="n">
+        <v>14977000</v>
+      </c>
+      <c r="I1117" s="5" t="n">
+        <v>19128</v>
       </c>
       <c r="J1117" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K1117" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L1117" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K1117" s="5" t="n">
+        <v>14977000</v>
+      </c>
+      <c r="L1117" s="5" t="n">
+        <v>19128</v>
       </c>
       <c r="M1117" s="3" t="inlineStr">
         <is>
@@ -76039,7 +76015,7 @@
       </c>
       <c r="N1117" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -86018,7 +85994,7 @@
       </c>
       <c r="G1266" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H1266" s="5" t="n">
@@ -87498,7 +87474,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -87508,7 +87484,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -88757,7 +88733,7 @@
           <t>D | 446呎 (2房)
 $724万
 $16,234/呎
-(26年-08月-14日)</t>
+(26年-09月-01日)</t>
         </is>
       </c>
       <c r="F30" s="20" t="inlineStr">
@@ -89230,12 +89206,12 @@
 (26年-08月-10日)</t>
         </is>
       </c>
-      <c r="F40" s="23" t="inlineStr">
+      <c r="F40" s="24" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
-$887万
-$19,280/呎
-(在售)</t>
+$754万
+$16,388/呎
+(26年-08月-30日)</t>
         </is>
       </c>
     </row>
@@ -89339,12 +89315,12 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B43" s="23" t="inlineStr">
+      <c r="B43" s="24" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
-$1008万
-$21,354/呎
-(在售)</t>
+$857万
+$18,151/呎
+(26年-08月-30日)</t>
         </is>
       </c>
       <c r="C43" s="20" t="inlineStr">
@@ -89574,12 +89550,12 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B48" s="23" t="inlineStr">
+      <c r="B48" s="24" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
-$996万
-$21,100/呎
-(在售)</t>
+$847万
+$17,935/呎
+(26年-08月-31日)</t>
         </is>
       </c>
       <c r="C48" s="20" t="inlineStr">
@@ -90115,12 +90091,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E59" s="23" t="inlineStr">
+      <c r="E59" s="24" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
-$822万
-$18,442/呎
-(在售)</t>
+$699万
+$15,675/呎
+(26年-08月-30日)</t>
         </is>
       </c>
       <c r="F59" s="23" t="inlineStr">
@@ -90253,7 +90229,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -90263,7 +90239,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -92026,12 +92002,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C36" s="23" t="inlineStr">
+      <c r="C36" s="24" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
-招标单位
--
-(在售)</t>
+$1254万
+$19,976/呎
+(26年-08月-31日)</t>
         </is>
       </c>
       <c r="D36" s="20" t="inlineStr">
@@ -93460,7 +93436,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>69</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -93470,7 +93446,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>89</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -94855,12 +94831,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E33" s="23" t="inlineStr">
+      <c r="E33" s="24" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
-$856万
-$19,231/呎
-(在售)</t>
+$727万
+$16,347/呎
+(26年-08月-31日)</t>
         </is>
       </c>
       <c r="F33" s="24" t="inlineStr">
@@ -94894,12 +94870,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D34" s="23" t="inlineStr">
+      <c r="D34" s="24" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
-$906万
-$18,555/呎
-(在售)</t>
+$788万
+$16,143/呎
+(26年-08月-31日)</t>
         </is>
       </c>
       <c r="E34" s="23" t="inlineStr">
@@ -94949,12 +94925,12 @@
 (26年-08月-28日)</t>
         </is>
       </c>
-      <c r="E35" s="23" t="inlineStr">
+      <c r="E35" s="24" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
-$852万
-$19,144/呎
-(在售)</t>
+$724万
+$16,272/呎
+(26年-08月-30日)</t>
         </is>
       </c>
       <c r="F35" s="24" t="inlineStr">
@@ -95356,12 +95332,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C44" s="23" t="inlineStr">
+      <c r="C44" s="24" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
-招标单位
--
-(在售)</t>
+$1090万
+$18,115/呎
+(26年-08月-31日)</t>
         </is>
       </c>
       <c r="D44" s="24" t="inlineStr">
@@ -95884,8 +95860,8 @@
       <c r="D55" s="24" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
-$765万
-$15,669/呎
+$746万
+$15,296/呎
 (26年-08月-14日)</t>
         </is>
       </c>
@@ -96077,12 +96053,12 @@
 (26年-08月-17日)</t>
         </is>
       </c>
-      <c r="E59" s="23" t="inlineStr">
+      <c r="E59" s="24" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
-$821万
-$18,440/呎
-(在售)</t>
+$714万
+$16,043/呎
+(26年-09月-01日)</t>
         </is>
       </c>
       <c r="F59" s="23" t="inlineStr">
@@ -96216,7 +96192,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>112</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -96226,7 +96202,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>65</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -98242,12 +98218,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C36" s="23" t="inlineStr">
+      <c r="C36" s="24" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
-招标单位
--
-(在售)</t>
+$1498万
+$19,128/呎
+(26年-08月-31日)</t>
         </is>
       </c>
       <c r="D36" s="23" t="inlineStr">
@@ -99673,7 +99649,7 @@
           <t>G | 457呎 (2房)
 $687万
 $15,025/呎
-(26年-08月-13日)</t>
+(26年-09月-01日)</t>
         </is>
       </c>
     </row>

--- a/web/files/九龙-将军澳-海瑅湾 II.xlsx
+++ b/web/files/九龙-将军澳-海瑅湾 II.xlsx
@@ -9064,7 +9064,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -17938,7 +17938,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H258" s="5" t="n">
@@ -32760,7 +32760,7 @@
       </c>
       <c r="G475" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H475" s="5" t="n">
@@ -51782,7 +51782,7 @@
       </c>
       <c r="G756" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H756" s="5" t="n">
@@ -56050,7 +56050,7 @@
       </c>
       <c r="G822" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H822" s="5" t="n">
@@ -58006,7 +58006,7 @@
       </c>
       <c r="G852" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H852" s="5" t="n">
@@ -58332,7 +58332,7 @@
       </c>
       <c r="G857" s="3" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H857" s="5" t="n">
@@ -60350,7 +60350,7 @@
       </c>
       <c r="G888" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H888" s="5" t="n">
@@ -73300,7 +73300,7 @@
       </c>
       <c r="G1077" s="3" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H1077" s="5" t="n">
@@ -76384,7 +76384,7 @@
       </c>
       <c r="G1123" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H1123" s="5" t="n">
@@ -78499,34 +78499,34 @@
       </c>
       <c r="F1155" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G1155" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H1155" s="5" t="n">
-        <v>7025000</v>
+        <v>5971200</v>
       </c>
       <c r="I1155" s="5" t="n">
-        <v>20245</v>
+        <v>17208</v>
       </c>
       <c r="J1155" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K1155" s="5" t="n">
-        <v>5971250</v>
+        <v>5971200</v>
       </c>
       <c r="L1155" s="5" t="n">
         <v>17208</v>
       </c>
       <c r="M1155" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N1155" s="3" t="inlineStr">
@@ -86468,7 +86468,7 @@
       </c>
       <c r="G1273" s="3" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H1273" s="5" t="n">
@@ -88686,7 +88686,7 @@
           <t>D | 446呎 (2房)
 $725万
 $16,259/呎
-(26年-08月-17日)</t>
+(26年-09月-03日)</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
@@ -89955,7 +89955,7 @@
           <t>D | 446呎 (2房)
 $712万
 $15,957/呎
-(26年-08月-15日)</t>
+(26年-09月-03日)</t>
         </is>
       </c>
       <c r="F56" s="24" t="inlineStr">
@@ -92078,7 +92078,7 @@
           <t>D | 554呎 (2房)
 $890万
 $16,067/呎
-(26年-08月-17日)</t>
+(26年-09月-03日)</t>
         </is>
       </c>
       <c r="F37" s="22" t="inlineStr">
@@ -94844,7 +94844,7 @@
           <t>E | 464呎 (2房)
 $740万
 $15,939/呎
-(26年-08月-22日)</t>
+(26年-09月-03日)</t>
         </is>
       </c>
     </row>
@@ -95447,7 +95447,7 @@
           <t>D | 445呎 (2房)
 $721万
 $16,198/呎
-(26年-08月-13日)</t>
+(26年-09月-03日)</t>
         </is>
       </c>
       <c r="F46" s="24" t="inlineStr">
@@ -95729,7 +95729,7 @@
           <t>D | 445呎 (2房)
 $698万
 $15,684/呎
-(26年-08月-14日)</t>
+(26年-09月-03日)</t>
         </is>
       </c>
       <c r="F52" s="24" t="inlineStr">
@@ -95776,7 +95776,7 @@
           <t>D | 445呎 (2房)
 $713万
 $16,027/呎
-(26年-08月-16日)</t>
+(26年-09月-03日)</t>
         </is>
       </c>
       <c r="F53" s="24" t="inlineStr">
@@ -96050,7 +96050,7 @@
           <t>C | 488呎 (2房)
 $741万
 $15,175/呎
-(26年-08月-17日)</t>
+(26年-09月-03日)</t>
         </is>
       </c>
       <c r="E59" s="24" t="inlineStr">
@@ -96192,7 +96192,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>111</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -96202,7 +96202,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>66</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -97948,7 +97948,7 @@
           <t>G | 457呎 (2房)
 $715万
 $15,651/呎
-(26年-08月-15日)</t>
+(26年-09月-03日)</t>
         </is>
       </c>
     </row>
@@ -98294,7 +98294,7 @@
           <t>C | 593呎 (2房)
 $1036万
 $17,472/呎
-(26年-08月-14日)</t>
+(26年-09月-03日)</t>
         </is>
       </c>
       <c r="E37" s="20" t="inlineStr">
@@ -98628,12 +98628,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G42" s="23" t="inlineStr">
+      <c r="G42" s="24" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
-$702万
-$20,245/呎
-(在售)</t>
+$597万
+$17,208/呎
+(26年-09月-02日)</t>
         </is>
       </c>
       <c r="H42" s="24" t="inlineStr">
@@ -99712,7 +99712,7 @@
           <t>G | 457呎 (2房)
 $701万
 $15,331/呎
-(26年-08月-16日)</t>
+(26年-09月-03日)</t>
         </is>
       </c>
     </row>
